--- a/test_group4_cut.xlsx
+++ b/test_group4_cut.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus Rog IGP\Documents\GeminiCLI101\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{001F5D9B-270C-49F6-BDDF-00B4390F4E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D503A96E-E1FF-48C1-9C77-BA374565E595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{06C1D2ED-63DE-4F2B-9D97-274982E1EB44}"/>
   </bookViews>
@@ -140,7 +140,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5615" uniqueCount="1336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5615" uniqueCount="1337">
   <si>
     <t>ลำดับ</t>
   </si>
@@ -4165,6 +4165,9 @@
   </si>
   <si>
     <t>ยกเลิก/ไม่มีการให้บริการแล้ว</t>
+  </si>
+  <si>
+    <t>อื่นๆ</t>
   </si>
 </sst>
 </file>
@@ -12802,7 +12805,7 @@
         <v>355</v>
       </c>
       <c r="F229" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G229" s="16" t="s">
         <v>356</v>
@@ -12825,7 +12828,7 @@
         <v>357</v>
       </c>
       <c r="F230" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G230" s="16" t="s">
         <v>356</v>
@@ -12894,7 +12897,7 @@
         <v>362</v>
       </c>
       <c r="F233" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G233" s="16" t="s">
         <v>363</v>
@@ -12986,7 +12989,7 @@
         <v>368</v>
       </c>
       <c r="F237" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G237" s="16" t="s">
         <v>369</v>
@@ -13055,7 +13058,7 @@
         <v>374</v>
       </c>
       <c r="F240" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G240" s="16" t="s">
         <v>356</v>
@@ -13078,7 +13081,7 @@
         <v>375</v>
       </c>
       <c r="F241" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G241" s="16" t="s">
         <v>349</v>
@@ -13101,7 +13104,7 @@
         <v>376</v>
       </c>
       <c r="F242" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G242" s="16" t="s">
         <v>349</v>
@@ -13124,7 +13127,7 @@
         <v>377</v>
       </c>
       <c r="F243" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G243" s="16" t="s">
         <v>349</v>
@@ -13147,7 +13150,7 @@
         <v>378</v>
       </c>
       <c r="F244" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G244" s="16" t="s">
         <v>349</v>
@@ -13170,7 +13173,7 @@
         <v>379</v>
       </c>
       <c r="F245" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G245" s="16" t="s">
         <v>380</v>
@@ -13492,7 +13495,7 @@
         <v>407</v>
       </c>
       <c r="F259" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G259" s="9" t="s">
         <v>408</v>
@@ -13515,7 +13518,7 @@
         <v>409</v>
       </c>
       <c r="F260" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G260" s="9" t="s">
         <v>408</v>
@@ -13538,7 +13541,7 @@
         <v>410</v>
       </c>
       <c r="F261" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G261" s="9" t="s">
         <v>408</v>
@@ -13561,7 +13564,7 @@
         <v>411</v>
       </c>
       <c r="F262" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G262" s="9" t="s">
         <v>408</v>
@@ -13584,7 +13587,7 @@
         <v>412</v>
       </c>
       <c r="F263" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G263" s="9" t="s">
         <v>408</v>
@@ -13607,7 +13610,7 @@
         <v>413</v>
       </c>
       <c r="F264" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G264" s="9" t="s">
         <v>408</v>
@@ -13653,7 +13656,7 @@
         <v>417</v>
       </c>
       <c r="F266" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G266" s="9" t="s">
         <v>418</v>
@@ -13676,7 +13679,7 @@
         <v>419</v>
       </c>
       <c r="F267" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G267" s="9" t="s">
         <v>420</v>
@@ -13699,7 +13702,7 @@
         <v>421</v>
       </c>
       <c r="F268" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G268" s="9" t="s">
         <v>422</v>
@@ -13722,7 +13725,7 @@
         <v>425</v>
       </c>
       <c r="F269" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G269" s="9"/>
     </row>
@@ -13766,7 +13769,7 @@
         <v>430</v>
       </c>
       <c r="F271" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G271" s="9" t="s">
         <v>431</v>
@@ -13789,7 +13792,7 @@
         <v>432</v>
       </c>
       <c r="F272" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G272" s="9" t="s">
         <v>433</v>
@@ -13812,7 +13815,7 @@
         <v>434</v>
       </c>
       <c r="F273" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G273" s="9" t="s">
         <v>435</v>
@@ -13835,7 +13838,7 @@
         <v>436</v>
       </c>
       <c r="F274" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G274" s="9" t="s">
         <v>437</v>
@@ -13950,7 +13953,7 @@
         <v>446</v>
       </c>
       <c r="F279" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G279" s="9" t="s">
         <v>447</v>
@@ -13973,7 +13976,7 @@
         <v>448</v>
       </c>
       <c r="F280" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G280" s="9" t="s">
         <v>447</v>
@@ -13996,7 +13999,7 @@
         <v>449</v>
       </c>
       <c r="F281" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G281" s="9" t="s">
         <v>447</v>
@@ -14019,7 +14022,7 @@
         <v>450</v>
       </c>
       <c r="F282" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G282" s="9" t="s">
         <v>447</v>
@@ -14042,7 +14045,7 @@
         <v>451</v>
       </c>
       <c r="F283" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G283" s="9" t="s">
         <v>447</v>
@@ -14065,7 +14068,7 @@
         <v>452</v>
       </c>
       <c r="F284" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G284" s="9" t="s">
         <v>447</v>
@@ -14088,7 +14091,7 @@
         <v>453</v>
       </c>
       <c r="F285" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G285" s="9" t="s">
         <v>447</v>
@@ -14111,7 +14114,7 @@
         <v>454</v>
       </c>
       <c r="F286" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G286" s="9" t="s">
         <v>447</v>
@@ -14134,7 +14137,7 @@
         <v>455</v>
       </c>
       <c r="F287" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G287" s="9" t="s">
         <v>447</v>
@@ -14157,7 +14160,7 @@
         <v>456</v>
       </c>
       <c r="F288" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G288" s="9" t="s">
         <v>447</v>
@@ -14180,7 +14183,7 @@
         <v>457</v>
       </c>
       <c r="F289" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G289" s="9" t="s">
         <v>447</v>
@@ -14203,7 +14206,7 @@
         <v>458</v>
       </c>
       <c r="F290" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G290" s="9" t="s">
         <v>459</v>
@@ -14226,7 +14229,7 @@
         <v>460</v>
       </c>
       <c r="F291" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G291" s="9" t="s">
         <v>459</v>
@@ -14249,7 +14252,7 @@
         <v>461</v>
       </c>
       <c r="F292" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G292" s="9" t="s">
         <v>459</v>
@@ -14272,7 +14275,7 @@
         <v>462</v>
       </c>
       <c r="F293" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G293" s="9" t="s">
         <v>447</v>
@@ -14295,7 +14298,7 @@
         <v>463</v>
       </c>
       <c r="F294" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G294" s="9" t="s">
         <v>459</v>
@@ -14318,7 +14321,7 @@
         <v>464</v>
       </c>
       <c r="F295" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G295" s="9" t="s">
         <v>459</v>
@@ -14341,7 +14344,7 @@
         <v>465</v>
       </c>
       <c r="F296" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G296" s="9" t="s">
         <v>459</v>
@@ -14364,7 +14367,7 @@
         <v>466</v>
       </c>
       <c r="F297" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G297" s="9" t="s">
         <v>459</v>
@@ -14387,7 +14390,7 @@
         <v>467</v>
       </c>
       <c r="F298" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G298" s="9" t="s">
         <v>459</v>
@@ -14410,7 +14413,7 @@
         <v>468</v>
       </c>
       <c r="F299" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G299" s="9" t="s">
         <v>459</v>
@@ -14433,7 +14436,7 @@
         <v>469</v>
       </c>
       <c r="F300" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G300" s="9" t="s">
         <v>459</v>
@@ -14456,7 +14459,7 @@
         <v>470</v>
       </c>
       <c r="F301" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G301" s="9" t="s">
         <v>459</v>
@@ -14479,7 +14482,7 @@
         <v>471</v>
       </c>
       <c r="F302" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G302" s="9" t="s">
         <v>459</v>
@@ -14502,7 +14505,7 @@
         <v>472</v>
       </c>
       <c r="F303" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G303" s="9" t="s">
         <v>459</v>
@@ -14525,7 +14528,7 @@
         <v>473</v>
       </c>
       <c r="F304" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G304" s="9" t="s">
         <v>459</v>
@@ -14548,7 +14551,7 @@
         <v>474</v>
       </c>
       <c r="F305" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G305" s="9" t="s">
         <v>459</v>
@@ -14571,7 +14574,7 @@
         <v>475</v>
       </c>
       <c r="F306" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G306" s="9" t="s">
         <v>459</v>
@@ -14824,7 +14827,7 @@
         <v>496</v>
       </c>
       <c r="F317" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G317" s="9" t="s">
         <v>497</v>
@@ -14847,7 +14850,7 @@
         <v>498</v>
       </c>
       <c r="F318" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G318" s="9" t="s">
         <v>497</v>
@@ -15353,7 +15356,7 @@
         <v>531</v>
       </c>
       <c r="F340" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G340" s="9" t="s">
         <v>532</v>
@@ -15397,7 +15400,7 @@
         <v>535</v>
       </c>
       <c r="F342" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G342" s="9" t="s">
         <v>536</v>
@@ -15420,7 +15423,7 @@
         <v>537</v>
       </c>
       <c r="F343" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G343" s="9" t="s">
         <v>536</v>
@@ -15443,7 +15446,7 @@
         <v>539</v>
       </c>
       <c r="F344" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G344" s="9" t="s">
         <v>540</v>
@@ -15489,7 +15492,7 @@
         <v>545</v>
       </c>
       <c r="F346" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G346" s="9" t="s">
         <v>546</v>
@@ -15512,7 +15515,7 @@
         <v>547</v>
       </c>
       <c r="F347" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G347" s="9" t="s">
         <v>546</v>
@@ -15535,7 +15538,7 @@
         <v>548</v>
       </c>
       <c r="F348" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G348" s="9" t="s">
         <v>546</v>
@@ -15558,7 +15561,7 @@
         <v>549</v>
       </c>
       <c r="F349" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G349" s="9" t="s">
         <v>546</v>
@@ -15667,7 +15670,7 @@
         <v>555</v>
       </c>
       <c r="F354" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G354" s="9" t="s">
         <v>546</v>
@@ -16175,7 +16178,7 @@
         <v>579</v>
       </c>
       <c r="F378" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G378" s="9" t="s">
         <v>546</v>
@@ -16219,7 +16222,7 @@
         <v>581</v>
       </c>
       <c r="F380" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G380" s="9" t="s">
         <v>546</v>
@@ -16242,7 +16245,7 @@
         <v>582</v>
       </c>
       <c r="F381" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G381" s="9" t="s">
         <v>546</v>
@@ -16265,7 +16268,7 @@
         <v>583</v>
       </c>
       <c r="F382" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G382" s="9" t="s">
         <v>546</v>
@@ -16288,7 +16291,7 @@
         <v>584</v>
       </c>
       <c r="F383" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G383" s="9" t="s">
         <v>546</v>
@@ -16378,7 +16381,7 @@
         <v>588</v>
       </c>
       <c r="F387" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G387" s="9" t="s">
         <v>546</v>
@@ -16401,7 +16404,7 @@
         <v>589</v>
       </c>
       <c r="F388" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G388" s="9" t="s">
         <v>546</v>
@@ -16447,7 +16450,7 @@
         <v>591</v>
       </c>
       <c r="F390" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G390" s="9" t="s">
         <v>546</v>
@@ -16470,7 +16473,7 @@
         <v>592</v>
       </c>
       <c r="F391" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G391" s="9" t="s">
         <v>546</v>
@@ -16493,7 +16496,7 @@
         <v>593</v>
       </c>
       <c r="F392" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G392" s="9" t="s">
         <v>546</v>
@@ -16516,7 +16519,7 @@
         <v>594</v>
       </c>
       <c r="F393" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G393" s="9" t="s">
         <v>546</v>
@@ -16539,7 +16542,7 @@
         <v>595</v>
       </c>
       <c r="F394" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G394" s="9" t="s">
         <v>546</v>
@@ -16562,7 +16565,7 @@
         <v>596</v>
       </c>
       <c r="F395" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G395" s="9" t="s">
         <v>546</v>
@@ -16585,7 +16588,7 @@
         <v>597</v>
       </c>
       <c r="F396" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G396" s="9" t="s">
         <v>546</v>
@@ -16608,7 +16611,7 @@
         <v>598</v>
       </c>
       <c r="F397" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G397" s="9" t="s">
         <v>546</v>
@@ -16631,7 +16634,7 @@
         <v>599</v>
       </c>
       <c r="F398" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G398" s="9" t="s">
         <v>546</v>
@@ -16654,7 +16657,7 @@
         <v>600</v>
       </c>
       <c r="F399" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G399" s="9" t="s">
         <v>546</v>
@@ -16868,7 +16871,7 @@
         <v>610</v>
       </c>
       <c r="F409" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G409" s="9" t="s">
         <v>546</v>
@@ -16891,7 +16894,7 @@
         <v>611</v>
       </c>
       <c r="F410" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G410" s="9" t="s">
         <v>546</v>
@@ -16914,7 +16917,7 @@
         <v>612</v>
       </c>
       <c r="F411" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G411" s="9" t="s">
         <v>546</v>
@@ -16937,7 +16940,7 @@
         <v>613</v>
       </c>
       <c r="F412" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G412" s="9" t="s">
         <v>546</v>
@@ -16960,7 +16963,7 @@
         <v>614</v>
       </c>
       <c r="F413" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G413" s="9" t="s">
         <v>546</v>
@@ -16983,7 +16986,7 @@
         <v>615</v>
       </c>
       <c r="F414" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G414" s="9" t="s">
         <v>546</v>
@@ -17006,7 +17009,7 @@
         <v>616</v>
       </c>
       <c r="F415" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G415" s="9" t="s">
         <v>546</v>
@@ -17029,7 +17032,7 @@
         <v>617</v>
       </c>
       <c r="F416" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G416" s="9" t="s">
         <v>546</v>
@@ -17052,7 +17055,7 @@
         <v>618</v>
       </c>
       <c r="F417" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G417" s="9" t="s">
         <v>546</v>
@@ -17075,7 +17078,7 @@
         <v>619</v>
       </c>
       <c r="F418" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G418" s="9" t="s">
         <v>546</v>
@@ -17098,7 +17101,7 @@
         <v>620</v>
       </c>
       <c r="F419" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G419" s="9" t="s">
         <v>546</v>
@@ -17121,7 +17124,7 @@
         <v>621</v>
       </c>
       <c r="F420" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G420" s="9" t="s">
         <v>546</v>
@@ -17144,7 +17147,7 @@
         <v>622</v>
       </c>
       <c r="F421" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G421" s="9" t="s">
         <v>546</v>
@@ -17167,7 +17170,7 @@
         <v>623</v>
       </c>
       <c r="F422" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G422" s="9" t="s">
         <v>546</v>
@@ -17190,7 +17193,7 @@
         <v>624</v>
       </c>
       <c r="F423" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G423" s="9" t="s">
         <v>546</v>
@@ -17213,7 +17216,7 @@
         <v>625</v>
       </c>
       <c r="F424" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G424" s="9" t="s">
         <v>546</v>
@@ -17236,7 +17239,7 @@
         <v>626</v>
       </c>
       <c r="F425" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G425" s="9" t="s">
         <v>546</v>
@@ -17259,7 +17262,7 @@
         <v>627</v>
       </c>
       <c r="F426" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G426" s="9" t="s">
         <v>546</v>
@@ -17282,7 +17285,7 @@
         <v>628</v>
       </c>
       <c r="F427" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G427" s="9" t="s">
         <v>546</v>
@@ -17305,7 +17308,7 @@
         <v>629</v>
       </c>
       <c r="F428" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G428" s="9" t="s">
         <v>546</v>
@@ -17328,7 +17331,7 @@
         <v>630</v>
       </c>
       <c r="F429" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G429" s="9" t="s">
         <v>546</v>
@@ -17351,7 +17354,7 @@
         <v>631</v>
       </c>
       <c r="F430" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G430" s="9" t="s">
         <v>546</v>
@@ -17374,7 +17377,7 @@
         <v>632</v>
       </c>
       <c r="F431" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G431" s="9" t="s">
         <v>546</v>
@@ -17397,7 +17400,7 @@
         <v>633</v>
       </c>
       <c r="F432" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G432" s="9" t="s">
         <v>546</v>
@@ -17420,7 +17423,7 @@
         <v>634</v>
       </c>
       <c r="F433" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G433" s="9" t="s">
         <v>546</v>
@@ -17443,7 +17446,7 @@
         <v>635</v>
       </c>
       <c r="F434" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G434" s="9" t="s">
         <v>546</v>
@@ -17466,7 +17469,7 @@
         <v>636</v>
       </c>
       <c r="F435" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G435" s="9" t="s">
         <v>546</v>
@@ -17489,7 +17492,7 @@
         <v>637</v>
       </c>
       <c r="F436" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G436" s="9" t="s">
         <v>546</v>
@@ -17512,7 +17515,7 @@
         <v>638</v>
       </c>
       <c r="F437" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G437" s="9" t="s">
         <v>546</v>
@@ -17535,7 +17538,7 @@
         <v>639</v>
       </c>
       <c r="F438" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G438" s="9" t="s">
         <v>546</v>
@@ -17558,7 +17561,7 @@
         <v>640</v>
       </c>
       <c r="F439" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G439" s="9" t="s">
         <v>546</v>
@@ -17581,7 +17584,7 @@
         <v>641</v>
       </c>
       <c r="F440" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G440" s="9" t="s">
         <v>546</v>
@@ -17604,7 +17607,7 @@
         <v>642</v>
       </c>
       <c r="F441" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G441" s="9" t="s">
         <v>546</v>
@@ -17627,7 +17630,7 @@
         <v>643</v>
       </c>
       <c r="F442" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G442" s="9" t="s">
         <v>546</v>
@@ -17650,7 +17653,7 @@
         <v>644</v>
       </c>
       <c r="F443" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G443" s="9" t="s">
         <v>546</v>
@@ -17673,7 +17676,7 @@
         <v>645</v>
       </c>
       <c r="F444" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G444" s="9" t="s">
         <v>546</v>
@@ -17696,7 +17699,7 @@
         <v>646</v>
       </c>
       <c r="F445" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G445" s="9" t="s">
         <v>546</v>
@@ -17719,7 +17722,7 @@
         <v>647</v>
       </c>
       <c r="F446" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G446" s="9" t="s">
         <v>546</v>
@@ -17763,7 +17766,7 @@
         <v>649</v>
       </c>
       <c r="F448" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G448" s="9" t="s">
         <v>650</v>
@@ -17786,7 +17789,7 @@
         <v>651</v>
       </c>
       <c r="F449" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G449" s="9" t="s">
         <v>650</v>
@@ -17809,7 +17812,7 @@
         <v>652</v>
       </c>
       <c r="F450" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G450" s="9" t="s">
         <v>650</v>
@@ -17855,7 +17858,7 @@
         <v>654</v>
       </c>
       <c r="F452" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G452" s="9" t="s">
         <v>546</v>
@@ -18035,7 +18038,7 @@
         <v>662</v>
       </c>
       <c r="F460" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G460" s="9" t="s">
         <v>546</v>
@@ -18142,7 +18145,7 @@
         <v>668</v>
       </c>
       <c r="F465" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G465" s="9" t="s">
         <v>669</v>
@@ -18333,7 +18336,7 @@
         <v>679</v>
       </c>
       <c r="F474" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G474" s="9" t="s">
         <v>680</v>
@@ -19070,7 +19073,7 @@
         <v>716</v>
       </c>
       <c r="F509" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G509" s="9" t="s">
         <v>717</v>
@@ -19093,7 +19096,7 @@
         <v>719</v>
       </c>
       <c r="F510" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G510" s="33" t="s">
         <v>720</v>
@@ -19116,7 +19119,7 @@
         <v>721</v>
       </c>
       <c r="F511" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G511" s="33" t="s">
         <v>720</v>
@@ -19139,7 +19142,7 @@
         <v>722</v>
       </c>
       <c r="F512" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G512" s="33" t="s">
         <v>720</v>
@@ -19162,7 +19165,7 @@
         <v>723</v>
       </c>
       <c r="F513" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G513" s="33" t="s">
         <v>720</v>
@@ -19185,7 +19188,7 @@
         <v>724</v>
       </c>
       <c r="F514" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G514" s="33" t="s">
         <v>720</v>
@@ -19208,7 +19211,7 @@
         <v>725</v>
       </c>
       <c r="F515" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G515" s="33" t="s">
         <v>726</v>
@@ -19231,7 +19234,7 @@
         <v>727</v>
       </c>
       <c r="F516" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G516" s="33" t="s">
         <v>726</v>
@@ -19254,7 +19257,7 @@
         <v>730</v>
       </c>
       <c r="F517" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G517" s="9" t="s">
         <v>731</v>
@@ -19300,7 +19303,7 @@
         <v>736</v>
       </c>
       <c r="F519" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G519" s="9"/>
     </row>
@@ -19321,7 +19324,7 @@
         <v>737</v>
       </c>
       <c r="F520" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G520" s="9" t="s">
         <v>131</v>
@@ -19344,7 +19347,7 @@
         <v>738</v>
       </c>
       <c r="F521" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G521" s="9" t="s">
         <v>131</v>
@@ -19367,7 +19370,7 @@
         <v>739</v>
       </c>
       <c r="F522" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G522" s="9" t="s">
         <v>131</v>
@@ -19390,7 +19393,7 @@
         <v>740</v>
       </c>
       <c r="F523" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G523" s="9" t="s">
         <v>131</v>
@@ -20022,7 +20025,7 @@
         <v>773</v>
       </c>
       <c r="F553" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G553" s="9" t="s">
         <v>774</v>
@@ -20045,7 +20048,7 @@
         <v>777</v>
       </c>
       <c r="F554" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G554" s="9" t="s">
         <v>778</v>
@@ -20068,7 +20071,7 @@
         <v>780</v>
       </c>
       <c r="F555" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G555" s="9" t="s">
         <v>781</v>
@@ -20091,7 +20094,7 @@
         <v>782</v>
       </c>
       <c r="F556" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G556" s="9" t="s">
         <v>781</v>
@@ -20114,7 +20117,7 @@
         <v>783</v>
       </c>
       <c r="F557" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G557" s="9" t="s">
         <v>781</v>
@@ -20137,7 +20140,7 @@
         <v>784</v>
       </c>
       <c r="F558" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G558" s="9" t="s">
         <v>781</v>
@@ -20160,7 +20163,7 @@
         <v>785</v>
       </c>
       <c r="F559" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G559" s="9" t="s">
         <v>781</v>
@@ -20183,7 +20186,7 @@
         <v>786</v>
       </c>
       <c r="F560" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G560" s="9" t="s">
         <v>781</v>
@@ -20206,7 +20209,7 @@
         <v>787</v>
       </c>
       <c r="F561" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G561" s="9" t="s">
         <v>781</v>
@@ -20229,7 +20232,7 @@
         <v>788</v>
       </c>
       <c r="F562" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G562" s="9" t="s">
         <v>781</v>
@@ -20252,7 +20255,7 @@
         <v>789</v>
       </c>
       <c r="F563" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G563" s="9" t="s">
         <v>781</v>
@@ -20275,7 +20278,7 @@
         <v>790</v>
       </c>
       <c r="F564" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G564" s="9" t="s">
         <v>781</v>
@@ -20298,7 +20301,7 @@
         <v>791</v>
       </c>
       <c r="F565" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G565" s="9" t="s">
         <v>781</v>
@@ -20321,7 +20324,7 @@
         <v>792</v>
       </c>
       <c r="F566" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G566" s="9" t="s">
         <v>781</v>
@@ -20344,7 +20347,7 @@
         <v>793</v>
       </c>
       <c r="F567" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G567" s="9" t="s">
         <v>781</v>
@@ -20367,7 +20370,7 @@
         <v>794</v>
       </c>
       <c r="F568" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G568" s="9" t="s">
         <v>781</v>
@@ -20390,7 +20393,7 @@
         <v>795</v>
       </c>
       <c r="F569" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G569" s="9" t="s">
         <v>781</v>
@@ -20413,7 +20416,7 @@
         <v>796</v>
       </c>
       <c r="F570" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G570" s="9" t="s">
         <v>781</v>
@@ -20436,7 +20439,7 @@
         <v>797</v>
       </c>
       <c r="F571" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G571" s="9" t="s">
         <v>781</v>
@@ -20459,7 +20462,7 @@
         <v>798</v>
       </c>
       <c r="F572" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G572" s="9" t="s">
         <v>781</v>
@@ -20482,7 +20485,7 @@
         <v>799</v>
       </c>
       <c r="F573" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G573" s="9" t="s">
         <v>781</v>
@@ -20505,7 +20508,7 @@
         <v>800</v>
       </c>
       <c r="F574" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G574" s="9" t="s">
         <v>781</v>
@@ -20528,7 +20531,7 @@
         <v>801</v>
       </c>
       <c r="F575" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G575" s="9" t="s">
         <v>781</v>
@@ -20551,7 +20554,7 @@
         <v>802</v>
       </c>
       <c r="F576" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G576" s="9" t="s">
         <v>781</v>
@@ -20574,7 +20577,7 @@
         <v>804</v>
       </c>
       <c r="F577" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G577" s="9" t="s">
         <v>805</v>
@@ -20597,7 +20600,7 @@
         <v>807</v>
       </c>
       <c r="F578" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G578" s="9" t="s">
         <v>808</v>
@@ -20735,7 +20738,7 @@
         <v>820</v>
       </c>
       <c r="F584" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G584" s="9" t="s">
         <v>821</v>
@@ -20804,7 +20807,7 @@
         <v>828</v>
       </c>
       <c r="F587" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G587" s="33" t="s">
         <v>829</v>
@@ -20827,7 +20830,7 @@
         <v>830</v>
       </c>
       <c r="F588" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G588" s="33" t="s">
         <v>829</v>
@@ -20850,7 +20853,7 @@
         <v>831</v>
       </c>
       <c r="F589" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G589" s="33" t="s">
         <v>829</v>
@@ -20896,7 +20899,7 @@
         <v>835</v>
       </c>
       <c r="F591" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G591" s="16" t="s">
         <v>836</v>
@@ -20919,7 +20922,7 @@
         <v>838</v>
       </c>
       <c r="F592" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G592" s="20" t="s">
         <v>839</v>
@@ -20942,7 +20945,7 @@
         <v>840</v>
       </c>
       <c r="F593" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G593" s="20" t="s">
         <v>839</v>
@@ -20965,7 +20968,7 @@
         <v>841</v>
       </c>
       <c r="F594" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G594" s="20" t="s">
         <v>839</v>
@@ -20988,7 +20991,7 @@
         <v>842</v>
       </c>
       <c r="F595" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G595" s="20" t="s">
         <v>839</v>
@@ -21011,7 +21014,7 @@
         <v>843</v>
       </c>
       <c r="F596" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G596" s="20" t="s">
         <v>839</v>
@@ -21034,7 +21037,7 @@
         <v>844</v>
       </c>
       <c r="F597" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G597" s="20" t="s">
         <v>839</v>
@@ -21057,7 +21060,7 @@
         <v>845</v>
       </c>
       <c r="F598" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G598" s="20" t="s">
         <v>839</v>
@@ -21080,7 +21083,7 @@
         <v>846</v>
       </c>
       <c r="F599" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G599" s="20" t="s">
         <v>839</v>
@@ -21103,7 +21106,7 @@
         <v>847</v>
       </c>
       <c r="F600" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G600" s="20" t="s">
         <v>839</v>
@@ -21126,7 +21129,7 @@
         <v>848</v>
       </c>
       <c r="F601" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G601" s="20" t="s">
         <v>839</v>
@@ -21149,7 +21152,7 @@
         <v>849</v>
       </c>
       <c r="F602" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G602" s="20" t="s">
         <v>839</v>
@@ -21172,7 +21175,7 @@
         <v>850</v>
       </c>
       <c r="F603" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G603" s="20" t="s">
         <v>839</v>
@@ -21195,7 +21198,7 @@
         <v>851</v>
       </c>
       <c r="F604" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G604" s="20" t="s">
         <v>839</v>
@@ -21218,7 +21221,7 @@
         <v>852</v>
       </c>
       <c r="F605" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G605" s="20" t="s">
         <v>839</v>
@@ -21241,7 +21244,7 @@
         <v>853</v>
       </c>
       <c r="F606" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G606" s="20" t="s">
         <v>839</v>
@@ -21264,7 +21267,7 @@
         <v>854</v>
       </c>
       <c r="F607" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G607" s="20" t="s">
         <v>839</v>
@@ -21287,7 +21290,7 @@
         <v>855</v>
       </c>
       <c r="F608" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G608" s="20" t="s">
         <v>839</v>
@@ -21310,7 +21313,7 @@
         <v>856</v>
       </c>
       <c r="F609" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G609" s="20" t="s">
         <v>839</v>
@@ -21333,7 +21336,7 @@
         <v>857</v>
       </c>
       <c r="F610" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G610" s="20" t="s">
         <v>839</v>
@@ -21356,7 +21359,7 @@
         <v>858</v>
       </c>
       <c r="F611" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G611" s="20" t="s">
         <v>839</v>
@@ -21379,7 +21382,7 @@
         <v>859</v>
       </c>
       <c r="F612" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G612" s="20" t="s">
         <v>839</v>
@@ -21402,7 +21405,7 @@
         <v>860</v>
       </c>
       <c r="F613" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G613" s="20" t="s">
         <v>839</v>
@@ -21425,7 +21428,7 @@
         <v>861</v>
       </c>
       <c r="F614" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G614" s="20" t="s">
         <v>839</v>
@@ -21448,7 +21451,7 @@
         <v>862</v>
       </c>
       <c r="F615" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G615" s="20" t="s">
         <v>839</v>
@@ -21471,7 +21474,7 @@
         <v>863</v>
       </c>
       <c r="F616" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G616" s="20" t="s">
         <v>839</v>
@@ -21494,7 +21497,7 @@
         <v>864</v>
       </c>
       <c r="F617" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G617" s="20" t="s">
         <v>839</v>
@@ -21517,7 +21520,7 @@
         <v>865</v>
       </c>
       <c r="F618" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G618" s="20" t="s">
         <v>839</v>
@@ -21540,7 +21543,7 @@
         <v>867</v>
       </c>
       <c r="F619" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G619" s="9" t="s">
         <v>781</v>
@@ -21563,7 +21566,7 @@
         <v>870</v>
       </c>
       <c r="F620" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G620" s="16" t="s">
         <v>871</v>
@@ -21586,7 +21589,7 @@
         <v>872</v>
       </c>
       <c r="F621" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G621" s="16" t="s">
         <v>871</v>
@@ -21609,7 +21612,7 @@
         <v>873</v>
       </c>
       <c r="F622" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G622" s="16" t="s">
         <v>871</v>
@@ -21632,7 +21635,7 @@
         <v>874</v>
       </c>
       <c r="F623" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G623" s="16" t="s">
         <v>875</v>
@@ -21655,7 +21658,7 @@
         <v>876</v>
       </c>
       <c r="F624" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G624" s="16" t="s">
         <v>875</v>
@@ -21678,7 +21681,7 @@
         <v>877</v>
       </c>
       <c r="F625" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G625" s="16" t="s">
         <v>875</v>
@@ -21701,7 +21704,7 @@
         <v>878</v>
       </c>
       <c r="F626" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G626" s="16" t="s">
         <v>875</v>
@@ -21724,7 +21727,7 @@
         <v>879</v>
       </c>
       <c r="F627" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G627" s="16" t="s">
         <v>871</v>
@@ -21747,7 +21750,7 @@
         <v>880</v>
       </c>
       <c r="F628" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G628" s="16" t="s">
         <v>875</v>
@@ -21770,7 +21773,7 @@
         <v>881</v>
       </c>
       <c r="F629" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G629" s="16" t="s">
         <v>875</v>
@@ -21793,7 +21796,7 @@
         <v>882</v>
       </c>
       <c r="F630" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G630" s="16" t="s">
         <v>875</v>
@@ -21816,7 +21819,7 @@
         <v>883</v>
       </c>
       <c r="F631" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G631" s="16" t="s">
         <v>871</v>
@@ -21839,7 +21842,7 @@
         <v>884</v>
       </c>
       <c r="F632" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G632" s="16" t="s">
         <v>871</v>
@@ -21862,7 +21865,7 @@
         <v>885</v>
       </c>
       <c r="F633" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G633" s="16" t="s">
         <v>871</v>
@@ -21931,7 +21934,7 @@
         <v>892</v>
       </c>
       <c r="F636" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G636" s="33" t="s">
         <v>893</v>
@@ -21954,7 +21957,7 @@
         <v>894</v>
       </c>
       <c r="F637" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G637" s="33" t="s">
         <v>893</v>
@@ -21977,7 +21980,7 @@
         <v>895</v>
       </c>
       <c r="F638" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G638" s="33" t="s">
         <v>893</v>
@@ -22023,7 +22026,7 @@
         <v>901</v>
       </c>
       <c r="F640" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G640" s="9" t="s">
         <v>902</v>
@@ -22046,7 +22049,7 @@
         <v>903</v>
       </c>
       <c r="F641" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G641" s="9" t="s">
         <v>902</v>
@@ -22069,7 +22072,7 @@
         <v>904</v>
       </c>
       <c r="F642" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G642" s="9" t="s">
         <v>902</v>
@@ -22092,7 +22095,7 @@
         <v>905</v>
       </c>
       <c r="F643" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G643" s="9" t="s">
         <v>902</v>
@@ -22184,7 +22187,7 @@
         <v>914</v>
       </c>
       <c r="F647" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G647" s="9" t="s">
         <v>915</v>
@@ -22207,7 +22210,7 @@
         <v>916</v>
       </c>
       <c r="F648" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G648" s="9" t="s">
         <v>915</v>
@@ -22230,7 +22233,7 @@
         <v>917</v>
       </c>
       <c r="F649" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G649" s="9" t="s">
         <v>915</v>
@@ -22253,7 +22256,7 @@
         <v>918</v>
       </c>
       <c r="F650" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G650" s="9" t="s">
         <v>915</v>
@@ -22387,7 +22390,7 @@
         <v>925</v>
       </c>
       <c r="F656" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G656" s="33" t="s">
         <v>926</v>
@@ -24611,7 +24614,7 @@
         <v>1032</v>
       </c>
       <c r="F760" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G760" s="27" t="s">
         <v>1033</v>
@@ -24933,7 +24936,7 @@
         <v>1047</v>
       </c>
       <c r="F774" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G774" s="27" t="s">
         <v>1048</v>
@@ -26474,7 +26477,7 @@
         <v>1119</v>
       </c>
       <c r="F841" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G841" s="9" t="s">
         <v>1120</v>
@@ -26520,7 +26523,7 @@
         <v>1122</v>
       </c>
       <c r="F843" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G843" s="9" t="s">
         <v>1120</v>
@@ -26566,7 +26569,7 @@
         <v>1124</v>
       </c>
       <c r="F845" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G845" s="9" t="s">
         <v>1120</v>
@@ -26589,7 +26592,7 @@
         <v>1125</v>
       </c>
       <c r="F846" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G846" s="9" t="s">
         <v>1126</v>
@@ -26612,7 +26615,7 @@
         <v>1127</v>
       </c>
       <c r="F847" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G847" s="9" t="s">
         <v>1126</v>
@@ -26635,7 +26638,7 @@
         <v>1128</v>
       </c>
       <c r="F848" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G848" s="9" t="s">
         <v>1126</v>
@@ -26658,7 +26661,7 @@
         <v>1129</v>
       </c>
       <c r="F849" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G849" s="9" t="s">
         <v>1126</v>
@@ -26681,7 +26684,7 @@
         <v>1130</v>
       </c>
       <c r="F850" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G850" s="9" t="s">
         <v>1126</v>
@@ -26704,7 +26707,7 @@
         <v>1131</v>
       </c>
       <c r="F851" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G851" s="9" t="s">
         <v>1126</v>
@@ -26727,7 +26730,7 @@
         <v>1132</v>
       </c>
       <c r="F852" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G852" s="9" t="s">
         <v>1120</v>
@@ -26750,7 +26753,7 @@
         <v>1133</v>
       </c>
       <c r="F853" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G853" s="9" t="s">
         <v>1126</v>
@@ -26911,7 +26914,7 @@
         <v>1150</v>
       </c>
       <c r="F860" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G860" s="9" t="s">
         <v>1151</v>
@@ -26934,7 +26937,7 @@
         <v>1152</v>
       </c>
       <c r="F861" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G861" s="9" t="s">
         <v>1151</v>
@@ -26957,7 +26960,7 @@
         <v>1153</v>
       </c>
       <c r="F862" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G862" s="9" t="s">
         <v>1151</v>
@@ -26980,7 +26983,7 @@
         <v>1155</v>
       </c>
       <c r="F863" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G863" s="9" t="s">
         <v>1156</v>
@@ -27003,7 +27006,7 @@
         <v>1158</v>
       </c>
       <c r="F864" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G864" s="9"/>
     </row>
@@ -27024,7 +27027,7 @@
         <v>1159</v>
       </c>
       <c r="F865" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G865" s="9"/>
     </row>
@@ -27045,7 +27048,7 @@
         <v>1160</v>
       </c>
       <c r="F866" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G866" s="9"/>
     </row>
@@ -27066,7 +27069,7 @@
         <v>1161</v>
       </c>
       <c r="F867" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G867" s="9"/>
     </row>
@@ -27087,7 +27090,7 @@
         <v>1163</v>
       </c>
       <c r="F868" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G868" s="9" t="s">
         <v>1164</v>
@@ -27110,7 +27113,7 @@
         <v>1165</v>
       </c>
       <c r="F869" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G869" s="9" t="s">
         <v>1164</v>
@@ -27133,7 +27136,7 @@
         <v>1166</v>
       </c>
       <c r="F870" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G870" s="9" t="s">
         <v>1164</v>
@@ -27156,7 +27159,7 @@
         <v>1169</v>
       </c>
       <c r="F871" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G871" s="9" t="s">
         <v>131</v>
@@ -27179,7 +27182,7 @@
         <v>1170</v>
       </c>
       <c r="F872" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G872" s="9" t="s">
         <v>131</v>
@@ -27202,7 +27205,7 @@
         <v>1171</v>
       </c>
       <c r="F873" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G873" s="9" t="s">
         <v>131</v>
@@ -27225,7 +27228,7 @@
         <v>1172</v>
       </c>
       <c r="F874" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G874" s="9" t="s">
         <v>131</v>
@@ -27248,7 +27251,7 @@
         <v>1173</v>
       </c>
       <c r="F875" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G875" s="9" t="s">
         <v>131</v>
@@ -27271,7 +27274,7 @@
         <v>1174</v>
       </c>
       <c r="F876" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G876" s="9" t="s">
         <v>131</v>
@@ -27294,7 +27297,7 @@
         <v>1175</v>
       </c>
       <c r="F877" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G877" s="9" t="s">
         <v>131</v>
@@ -27317,7 +27320,7 @@
         <v>1176</v>
       </c>
       <c r="F878" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G878" s="9" t="s">
         <v>131</v>
@@ -27340,7 +27343,7 @@
         <v>1177</v>
       </c>
       <c r="F879" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G879" s="9" t="s">
         <v>131</v>
@@ -27363,7 +27366,7 @@
         <v>1178</v>
       </c>
       <c r="F880" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G880" s="9" t="s">
         <v>131</v>
@@ -27386,7 +27389,7 @@
         <v>1179</v>
       </c>
       <c r="F881" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G881" s="9" t="s">
         <v>131</v>
@@ -27409,7 +27412,7 @@
         <v>1180</v>
       </c>
       <c r="F882" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G882" s="9" t="s">
         <v>131</v>
@@ -27432,7 +27435,7 @@
         <v>1181</v>
       </c>
       <c r="F883" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G883" s="9" t="s">
         <v>131</v>
@@ -27455,7 +27458,7 @@
         <v>1182</v>
       </c>
       <c r="F884" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G884" s="9" t="s">
         <v>131</v>
@@ -27478,7 +27481,7 @@
         <v>1184</v>
       </c>
       <c r="F885" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G885" s="9" t="s">
         <v>1185</v>
@@ -27501,7 +27504,7 @@
         <v>1186</v>
       </c>
       <c r="F886" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G886" s="9" t="s">
         <v>1187</v>
@@ -27524,7 +27527,7 @@
         <v>1189</v>
       </c>
       <c r="F887" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G887" s="33" t="s">
         <v>1190</v>
@@ -27547,7 +27550,7 @@
         <v>1191</v>
       </c>
       <c r="F888" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G888" s="33" t="s">
         <v>1190</v>
@@ -27570,7 +27573,7 @@
         <v>1192</v>
       </c>
       <c r="F889" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G889" s="33" t="s">
         <v>1190</v>
@@ -27593,7 +27596,7 @@
         <v>1193</v>
       </c>
       <c r="F890" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G890" s="33" t="s">
         <v>1190</v>
@@ -27616,7 +27619,7 @@
         <v>1194</v>
       </c>
       <c r="F891" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G891" s="33" t="s">
         <v>1190</v>
@@ -27639,7 +27642,7 @@
         <v>1195</v>
       </c>
       <c r="F892" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G892" s="33" t="s">
         <v>1190</v>
@@ -27662,7 +27665,7 @@
         <v>1196</v>
       </c>
       <c r="F893" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G893" s="9" t="s">
         <v>1197</v>
@@ -27685,7 +27688,7 @@
         <v>1198</v>
       </c>
       <c r="F894" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G894" s="33" t="s">
         <v>1190</v>
@@ -27869,7 +27872,7 @@
         <v>1213</v>
       </c>
       <c r="F902" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G902" s="9" t="s">
         <v>131</v>
@@ -27892,7 +27895,7 @@
         <v>1214</v>
       </c>
       <c r="F903" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G903" s="9" t="s">
         <v>131</v>
@@ -28076,7 +28079,7 @@
         <v>1229</v>
       </c>
       <c r="F911" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G911" s="9" t="s">
         <v>1230</v>
@@ -29364,7 +29367,7 @@
         <v>1314</v>
       </c>
       <c r="F967" s="8" t="s">
-        <v>11</v>
+        <v>1336</v>
       </c>
       <c r="G967" s="9" t="s">
         <v>1315</v>

--- a/test_group4_cut.xlsx
+++ b/test_group4_cut.xlsx
@@ -8,34 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus Rog IGP\Documents\GeminiCLI101\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D503A96E-E1FF-48C1-9C77-BA374565E595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9907C765-C515-43DC-A5AA-9879953839DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{06C1D2ED-63DE-4F2B-9D97-274982E1EB44}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{06C1D2ED-63DE-4F2B-9D97-274982E1EB44}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
-    <sheet name="กลุ่ม4จะไม่เป็นe" sheetId="1" r:id="rId2"/>
+    <sheet name="กลุ่ม4จะไม่เป็นe" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">กลุ่ม4จะไม่เป็นe!$B$1:$G$978</definedName>
-    <definedName name="_xlcn.WorksheetConnection_test_group4_cut.xlsxTable1101" hidden="1">Table110[]</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">กลุ่ม4จะไม่เป็นe!$B$1:$G$978</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <pivotCaches>
-    <pivotCache cacheId="174" r:id="rId3"/>
-    <pivotCache cacheId="175" r:id="rId4"/>
-    <pivotCache cacheId="187" r:id="rId5"/>
-  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{FCE2AD5D-F65C-4FA6-A056-5C36A1767C68}">
-      <x15:dataModel>
-        <x15:modelTables>
-          <x15:modelTable id="Table110" name="Table110" connection="WorksheetConnection_test_group4_cut.xlsx!Table110"/>
-        </x15:modelTables>
-      </x15:dataModel>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -116,31 +102,8 @@
 </comments>
 </file>
 
-<file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{4B96C08A-9767-47DA-B632-2261221CAD2D}" keepAlive="1" name="ThisWorkbookDataModel" description="Data Model" type="5" refreshedVersion="8" minRefreshableVersion="5" background="1">
-    <dbPr connection="Data Model Connection" command="Model" commandType="1"/>
-    <olapPr sendLocale="1" rowDrillCount="1000"/>
-    <extLst>
-      <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
-        <x15:connection id="" model="1"/>
-      </ext>
-    </extLst>
-  </connection>
-  <connection id="2" xr16:uid="{506CBDED-1140-4C4B-B8BC-AF13F9396824}" name="WorksheetConnection_test_group4_cut.xlsx!Table110" type="102" refreshedVersion="8" minRefreshableVersion="5">
-    <extLst>
-      <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
-        <x15:connection id="Table110" autoDelete="1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_test_group4_cut.xlsxTable1101"/>
-        </x15:connection>
-      </ext>
-    </extLst>
-  </connection>
-</connections>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5615" uniqueCount="1337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5612" uniqueCount="1334">
   <si>
     <t>ลำดับ</t>
   </si>
@@ -4153,15 +4116,6 @@
   </si>
   <si>
     <t>มีผู้ใบอนุมัติบัตรและวุฒิบัตรฯ ฉบับภาษาอังกฤษ จำนวนน้อย 1 ปี จำนวนไม่เกิน 10 คน</t>
-  </si>
-  <si>
-    <t>Distinct Count of รายชื่อหน่วยงาน</t>
-  </si>
-  <si>
-    <t>Distinct Count of รายชื่อกระทรวง</t>
-  </si>
-  <si>
-    <t>Count of ชื่อกระบวนงาน (รายกรณี)</t>
   </si>
   <si>
     <t>ยกเลิก/ไม่มีการให้บริการแล้ว</t>
@@ -4348,7 +4302,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4447,7 +4401,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -6751,408 +6704,6 @@
 </inkml:ink>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Asus Rog IGP" refreshedDate="46145.528856712961" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{1BD1660A-7130-407F-AA49-7594F9F44174}">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="1">
-    <cacheField name="[Measures].[Distinct Count of รายชื่อกระทรวง]" caption="Distinct Count of รายชื่อกระทรวง" numFmtId="0" hierarchy="12" level="32767"/>
-  </cacheFields>
-  <cacheHierarchies count="15">
-    <cacheHierarchy uniqueName="[Table110].[ลำดับ]" caption="ลำดับ" attribute="1" defaultMemberUniqueName="[Table110].[ลำดับ].[All]" allUniqueName="[Table110].[ลำดับ].[All]" dimensionUniqueName="[Table110]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table110].[รายชื่อกระทรวง]" caption="รายชื่อกระทรวง" attribute="1" defaultMemberUniqueName="[Table110].[รายชื่อกระทรวง].[All]" allUniqueName="[Table110].[รายชื่อกระทรวง].[All]" dimensionUniqueName="[Table110]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table110].[รายชื่อหน่วยงาน]" caption="รายชื่อหน่วยงาน" attribute="1" defaultMemberUniqueName="[Table110].[รายชื่อหน่วยงาน].[All]" allUniqueName="[Table110].[รายชื่อหน่วยงาน].[All]" dimensionUniqueName="[Table110]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table110].[ประเภทหน่วยงาน]" caption="ประเภทหน่วยงาน" attribute="1" defaultMemberUniqueName="[Table110].[ประเภทหน่วยงาน].[All]" allUniqueName="[Table110].[ประเภทหน่วยงาน].[All]" dimensionUniqueName="[Table110]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table110].[ชื่อกระบวนงาน (รายกรณี)]" caption="ชื่อกระบวนงาน (รายกรณี)" attribute="1" defaultMemberUniqueName="[Table110].[ชื่อกระบวนงาน (รายกรณี)].[All]" allUniqueName="[Table110].[ชื่อกระบวนงาน (รายกรณี)].[All]" dimensionUniqueName="[Table110]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table110].[เหตุผลที่ไม่พัฒนาเป็น e-Service]" caption="เหตุผลที่ไม่พัฒนาเป็น e-Service" attribute="1" defaultMemberUniqueName="[Table110].[เหตุผลที่ไม่พัฒนาเป็น e-Service].[All]" allUniqueName="[Table110].[เหตุผลที่ไม่พัฒนาเป็น e-Service].[All]" dimensionUniqueName="[Table110]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table110].[รายละเอียด  (เหตุผลที่ไม่พัฒนาเป็น e-Service)]" caption="รายละเอียด  (เหตุผลที่ไม่พัฒนาเป็น e-Service)" attribute="1" defaultMemberUniqueName="[Table110].[รายละเอียด  (เหตุผลที่ไม่พัฒนาเป็น e-Service)].[All]" allUniqueName="[Table110].[รายละเอียด  (เหตุผลที่ไม่พัฒนาเป็น e-Service)].[All]" dimensionUniqueName="[Table110]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Table110]" caption="__XL_Count Table110" measure="1" displayFolder="" measureGroup="Table110" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Count of รายชื่อหน่วยงาน]" caption="Count of รายชื่อหน่วยงาน" measure="1" displayFolder="" measureGroup="Table110" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="2"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Distinct Count of รายชื่อหน่วยงาน]" caption="Distinct Count of รายชื่อหน่วยงาน" measure="1" displayFolder="" measureGroup="Table110" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="2"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Count of รายชื่อกระทรวง]" caption="Count of รายชื่อกระทรวง" measure="1" displayFolder="" measureGroup="Table110" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="1"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Distinct Count of รายชื่อกระทรวง]" caption="Distinct Count of รายชื่อกระทรวง" measure="1" displayFolder="" measureGroup="Table110" count="0" oneField="1" hidden="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="1"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Sum of ลำดับ]" caption="Sum of ลำดับ" measure="1" displayFolder="" measureGroup="Table110" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="0"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Count of ชื่อกระบวนงาน (รายกรณี)]" caption="Count of ชื่อกระบวนงาน (รายกรณี)" measure="1" displayFolder="" measureGroup="Table110" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="4"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="2">
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-    <dimension name="Table110" uniqueName="[Table110]" caption="Table110"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Table110" caption="Table110"/>
-  </measureGroups>
-  <maps count="1">
-    <map measureGroup="0" dimension="1"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Asus Rog IGP" refreshedDate="46145.52228287037" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{7B2C76E5-FD55-4835-A736-980F6EE3ACB6}">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="1">
-    <cacheField name="[Measures].[Distinct Count of รายชื่อหน่วยงาน]" caption="Distinct Count of รายชื่อหน่วยงาน" numFmtId="0" hierarchy="10" level="32767"/>
-  </cacheFields>
-  <cacheHierarchies count="15">
-    <cacheHierarchy uniqueName="[Table110].[ลำดับ]" caption="ลำดับ" attribute="1" defaultMemberUniqueName="[Table110].[ลำดับ].[All]" allUniqueName="[Table110].[ลำดับ].[All]" dimensionUniqueName="[Table110]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table110].[รายชื่อกระทรวง]" caption="รายชื่อกระทรวง" attribute="1" defaultMemberUniqueName="[Table110].[รายชื่อกระทรวง].[All]" allUniqueName="[Table110].[รายชื่อกระทรวง].[All]" dimensionUniqueName="[Table110]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table110].[รายชื่อหน่วยงาน]" caption="รายชื่อหน่วยงาน" attribute="1" defaultMemberUniqueName="[Table110].[รายชื่อหน่วยงาน].[All]" allUniqueName="[Table110].[รายชื่อหน่วยงาน].[All]" dimensionUniqueName="[Table110]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table110].[ประเภทหน่วยงาน]" caption="ประเภทหน่วยงาน" attribute="1" defaultMemberUniqueName="[Table110].[ประเภทหน่วยงาน].[All]" allUniqueName="[Table110].[ประเภทหน่วยงาน].[All]" dimensionUniqueName="[Table110]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table110].[ชื่อกระบวนงาน (รายกรณี)]" caption="ชื่อกระบวนงาน (รายกรณี)" attribute="1" defaultMemberUniqueName="[Table110].[ชื่อกระบวนงาน (รายกรณี)].[All]" allUniqueName="[Table110].[ชื่อกระบวนงาน (รายกรณี)].[All]" dimensionUniqueName="[Table110]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table110].[เหตุผลที่ไม่พัฒนาเป็น e-Service]" caption="เหตุผลที่ไม่พัฒนาเป็น e-Service" attribute="1" defaultMemberUniqueName="[Table110].[เหตุผลที่ไม่พัฒนาเป็น e-Service].[All]" allUniqueName="[Table110].[เหตุผลที่ไม่พัฒนาเป็น e-Service].[All]" dimensionUniqueName="[Table110]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table110].[รายละเอียด  (เหตุผลที่ไม่พัฒนาเป็น e-Service)]" caption="รายละเอียด  (เหตุผลที่ไม่พัฒนาเป็น e-Service)" attribute="1" defaultMemberUniqueName="[Table110].[รายละเอียด  (เหตุผลที่ไม่พัฒนาเป็น e-Service)].[All]" allUniqueName="[Table110].[รายละเอียด  (เหตุผลที่ไม่พัฒนาเป็น e-Service)].[All]" dimensionUniqueName="[Table110]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Table110]" caption="__XL_Count Table110" measure="1" displayFolder="" measureGroup="Table110" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Count of รายชื่อหน่วยงาน]" caption="Count of รายชื่อหน่วยงาน" measure="1" displayFolder="" measureGroup="Table110" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="2"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Distinct Count of รายชื่อหน่วยงาน]" caption="Distinct Count of รายชื่อหน่วยงาน" measure="1" displayFolder="" measureGroup="Table110" count="0" oneField="1" hidden="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="2"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Count of รายชื่อกระทรวง]" caption="Count of รายชื่อกระทรวง" measure="1" displayFolder="" measureGroup="Table110" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="1"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Distinct Count of รายชื่อกระทรวง]" caption="Distinct Count of รายชื่อกระทรวง" measure="1" displayFolder="" measureGroup="Table110" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="1"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Sum of ลำดับ]" caption="Sum of ลำดับ" measure="1" displayFolder="" measureGroup="Table110" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="0"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Count of ชื่อกระบวนงาน (รายกรณี)]" caption="Count of ชื่อกระบวนงาน (รายกรณี)" measure="1" displayFolder="" measureGroup="Table110" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="4"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="2">
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-    <dimension name="Table110" uniqueName="[Table110]" caption="Table110"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Table110" caption="Table110"/>
-  </measureGroups>
-  <maps count="1">
-    <map measureGroup="0" dimension="1"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Asus Rog IGP" refreshedDate="46145.529248611114" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{14612A43-FF21-4FEC-AD14-692B6680D3FF}">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="1">
-    <cacheField name="[Measures].[Count of ชื่อกระบวนงาน (รายกรณี)]" caption="Count of ชื่อกระบวนงาน (รายกรณี)" numFmtId="0" hierarchy="14" level="32767"/>
-  </cacheFields>
-  <cacheHierarchies count="15">
-    <cacheHierarchy uniqueName="[Table110].[ลำดับ]" caption="ลำดับ" attribute="1" defaultMemberUniqueName="[Table110].[ลำดับ].[All]" allUniqueName="[Table110].[ลำดับ].[All]" dimensionUniqueName="[Table110]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table110].[รายชื่อกระทรวง]" caption="รายชื่อกระทรวง" attribute="1" defaultMemberUniqueName="[Table110].[รายชื่อกระทรวง].[All]" allUniqueName="[Table110].[รายชื่อกระทรวง].[All]" dimensionUniqueName="[Table110]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table110].[รายชื่อหน่วยงาน]" caption="รายชื่อหน่วยงาน" attribute="1" defaultMemberUniqueName="[Table110].[รายชื่อหน่วยงาน].[All]" allUniqueName="[Table110].[รายชื่อหน่วยงาน].[All]" dimensionUniqueName="[Table110]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table110].[ประเภทหน่วยงาน]" caption="ประเภทหน่วยงาน" attribute="1" defaultMemberUniqueName="[Table110].[ประเภทหน่วยงาน].[All]" allUniqueName="[Table110].[ประเภทหน่วยงาน].[All]" dimensionUniqueName="[Table110]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table110].[ชื่อกระบวนงาน (รายกรณี)]" caption="ชื่อกระบวนงาน (รายกรณี)" attribute="1" defaultMemberUniqueName="[Table110].[ชื่อกระบวนงาน (รายกรณี)].[All]" allUniqueName="[Table110].[ชื่อกระบวนงาน (รายกรณี)].[All]" dimensionUniqueName="[Table110]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table110].[เหตุผลที่ไม่พัฒนาเป็น e-Service]" caption="เหตุผลที่ไม่พัฒนาเป็น e-Service" attribute="1" defaultMemberUniqueName="[Table110].[เหตุผลที่ไม่พัฒนาเป็น e-Service].[All]" allUniqueName="[Table110].[เหตุผลที่ไม่พัฒนาเป็น e-Service].[All]" dimensionUniqueName="[Table110]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table110].[รายละเอียด  (เหตุผลที่ไม่พัฒนาเป็น e-Service)]" caption="รายละเอียด  (เหตุผลที่ไม่พัฒนาเป็น e-Service)" attribute="1" defaultMemberUniqueName="[Table110].[รายละเอียด  (เหตุผลที่ไม่พัฒนาเป็น e-Service)].[All]" allUniqueName="[Table110].[รายละเอียด  (เหตุผลที่ไม่พัฒนาเป็น e-Service)].[All]" dimensionUniqueName="[Table110]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Table110]" caption="__XL_Count Table110" measure="1" displayFolder="" measureGroup="Table110" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Count of รายชื่อหน่วยงาน]" caption="Count of รายชื่อหน่วยงาน" measure="1" displayFolder="" measureGroup="Table110" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="2"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Distinct Count of รายชื่อหน่วยงาน]" caption="Distinct Count of รายชื่อหน่วยงาน" measure="1" displayFolder="" measureGroup="Table110" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="2"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Count of รายชื่อกระทรวง]" caption="Count of รายชื่อกระทรวง" measure="1" displayFolder="" measureGroup="Table110" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="1"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Distinct Count of รายชื่อกระทรวง]" caption="Distinct Count of รายชื่อกระทรวง" measure="1" displayFolder="" measureGroup="Table110" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="1"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Sum of ลำดับ]" caption="Sum of ลำดับ" measure="1" displayFolder="" measureGroup="Table110" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="0"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Count of ชื่อกระบวนงาน (รายกรณี)]" caption="Count of ชื่อกระบวนงาน (รายกรณี)" measure="1" displayFolder="" measureGroup="Table110" count="0" oneField="1" hidden="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="4"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="2">
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-    <dimension name="Table110" uniqueName="[Table110]" caption="Table110"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Table110" caption="Table110"/>
-  </measureGroups>
-  <maps count="1">
-    <map measureGroup="0" dimension="1"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6BDDB2C7-B0B9-424D-A91F-90CA010E08E6}" name="PivotTable9" cacheId="187" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A9:A10" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="1">
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of ชื่อกระบวนงาน (รายกรณี)" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotHierarchies count="15">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1" caption="Distinct Count of รายชื่อหน่วยงาน"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1" caption="Distinct Count of รายชื่อกระทรวง"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_test_group4_cut.xlsx!Table110">
-        <x15:activeTabTopLevelEntity name="[Table110]"/>
-      </x15:pivotTableUISettings>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F1702B1B-6C25-4596-9B4C-6F589329BCB5}" name="PivotTable8" cacheId="174" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A6:A7" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="1">
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Distinct Count of รายชื่อกระทรวง" fld="0" subtotal="count" baseField="0" baseItem="0">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{FABC7310-3BB5-11E1-824E-6D434824019B}">
-          <x15:dataField isCountDistinct="1"/>
-        </ext>
-      </extLst>
-    </dataField>
-  </dataFields>
-  <pivotHierarchies count="15">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1" caption="Distinct Count of รายชื่อหน่วยงาน"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1" caption="Distinct Count of รายชื่อกระทรวง"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_test_group4_cut.xlsx!Table110">
-        <x15:activeTabTopLevelEntity name="[Table110]"/>
-      </x15:pivotTableUISettings>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DF7DACEF-0EE7-466E-AAA3-8956070D67B9}" name="PivotTable7" cacheId="175" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:A4" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="1">
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Distinct Count of รายชื่อหน่วยงาน" fld="0" subtotal="count" baseField="0" baseItem="0">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{FABC7310-3BB5-11E1-824E-6D434824019B}">
-          <x15:dataField isCountDistinct="1"/>
-        </ext>
-      </extLst>
-    </dataField>
-  </dataFields>
-  <pivotHierarchies count="15">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1" caption="Distinct Count of รายชื่อหน่วยงาน"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_test_group4_cut.xlsx!Table110">
-        <x15:activeTabTopLevelEntity name="[Table110]"/>
-      </x15:pivotTableUISettings>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5A16785F-1445-424B-8023-A1706DCEF7F8}" name="Table110" displayName="Table110" ref="A1:G978" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16" headerRowBorderDxfId="26" tableBorderDxfId="27" totalsRowBorderDxfId="25">
   <autoFilter ref="A1:G978" xr:uid="{B36BA02D-2E6A-4F83-BFCB-32146121612C}"/>
@@ -7485,50 +7036,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AA40D42-C910-49C5-BD9C-702ED346032B}">
-  <dimension ref="A3:A10"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.25" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>1332</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A4" s="36">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A7" s="36">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>1334</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A10" s="36">
-        <v>977</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB05268-03BA-49E4-9C0D-981EBBC6D969}">
   <dimension ref="A1:G979"/>
   <sheetFormatPr defaultColWidth="11.6640625" defaultRowHeight="21" x14ac:dyDescent="0.7"/>
@@ -12759,7 +12266,7 @@
         <v>352</v>
       </c>
       <c r="F227" s="7" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
       <c r="G227" s="20" t="s">
         <v>353</v>
@@ -12782,7 +12289,7 @@
         <v>354</v>
       </c>
       <c r="F228" s="7" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
       <c r="G228" s="20" t="s">
         <v>353</v>
@@ -12805,7 +12312,7 @@
         <v>355</v>
       </c>
       <c r="F229" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G229" s="16" t="s">
         <v>356</v>
@@ -12828,7 +12335,7 @@
         <v>357</v>
       </c>
       <c r="F230" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G230" s="16" t="s">
         <v>356</v>
@@ -12897,7 +12404,7 @@
         <v>362</v>
       </c>
       <c r="F233" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G233" s="16" t="s">
         <v>363</v>
@@ -12989,7 +12496,7 @@
         <v>368</v>
       </c>
       <c r="F237" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G237" s="16" t="s">
         <v>369</v>
@@ -13058,7 +12565,7 @@
         <v>374</v>
       </c>
       <c r="F240" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G240" s="16" t="s">
         <v>356</v>
@@ -13081,7 +12588,7 @@
         <v>375</v>
       </c>
       <c r="F241" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G241" s="16" t="s">
         <v>349</v>
@@ -13104,7 +12611,7 @@
         <v>376</v>
       </c>
       <c r="F242" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G242" s="16" t="s">
         <v>349</v>
@@ -13127,7 +12634,7 @@
         <v>377</v>
       </c>
       <c r="F243" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G243" s="16" t="s">
         <v>349</v>
@@ -13150,7 +12657,7 @@
         <v>378</v>
       </c>
       <c r="F244" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G244" s="16" t="s">
         <v>349</v>
@@ -13173,7 +12680,7 @@
         <v>379</v>
       </c>
       <c r="F245" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G245" s="16" t="s">
         <v>380</v>
@@ -13495,7 +13002,7 @@
         <v>407</v>
       </c>
       <c r="F259" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G259" s="9" t="s">
         <v>408</v>
@@ -13518,7 +13025,7 @@
         <v>409</v>
       </c>
       <c r="F260" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G260" s="9" t="s">
         <v>408</v>
@@ -13541,7 +13048,7 @@
         <v>410</v>
       </c>
       <c r="F261" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G261" s="9" t="s">
         <v>408</v>
@@ -13564,7 +13071,7 @@
         <v>411</v>
       </c>
       <c r="F262" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G262" s="9" t="s">
         <v>408</v>
@@ -13587,7 +13094,7 @@
         <v>412</v>
       </c>
       <c r="F263" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G263" s="9" t="s">
         <v>408</v>
@@ -13610,7 +13117,7 @@
         <v>413</v>
       </c>
       <c r="F264" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G264" s="9" t="s">
         <v>408</v>
@@ -13656,7 +13163,7 @@
         <v>417</v>
       </c>
       <c r="F266" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G266" s="9" t="s">
         <v>418</v>
@@ -13679,7 +13186,7 @@
         <v>419</v>
       </c>
       <c r="F267" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G267" s="9" t="s">
         <v>420</v>
@@ -13702,7 +13209,7 @@
         <v>421</v>
       </c>
       <c r="F268" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G268" s="9" t="s">
         <v>422</v>
@@ -13725,7 +13232,7 @@
         <v>425</v>
       </c>
       <c r="F269" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G269" s="9"/>
     </row>
@@ -13769,7 +13276,7 @@
         <v>430</v>
       </c>
       <c r="F271" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G271" s="9" t="s">
         <v>431</v>
@@ -13792,7 +13299,7 @@
         <v>432</v>
       </c>
       <c r="F272" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G272" s="9" t="s">
         <v>433</v>
@@ -13815,7 +13322,7 @@
         <v>434</v>
       </c>
       <c r="F273" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G273" s="9" t="s">
         <v>435</v>
@@ -13838,7 +13345,7 @@
         <v>436</v>
       </c>
       <c r="F274" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G274" s="9" t="s">
         <v>437</v>
@@ -13953,7 +13460,7 @@
         <v>446</v>
       </c>
       <c r="F279" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G279" s="9" t="s">
         <v>447</v>
@@ -13976,7 +13483,7 @@
         <v>448</v>
       </c>
       <c r="F280" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G280" s="9" t="s">
         <v>447</v>
@@ -13999,7 +13506,7 @@
         <v>449</v>
       </c>
       <c r="F281" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G281" s="9" t="s">
         <v>447</v>
@@ -14022,7 +13529,7 @@
         <v>450</v>
       </c>
       <c r="F282" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G282" s="9" t="s">
         <v>447</v>
@@ -14045,7 +13552,7 @@
         <v>451</v>
       </c>
       <c r="F283" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G283" s="9" t="s">
         <v>447</v>
@@ -14068,7 +13575,7 @@
         <v>452</v>
       </c>
       <c r="F284" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G284" s="9" t="s">
         <v>447</v>
@@ -14091,7 +13598,7 @@
         <v>453</v>
       </c>
       <c r="F285" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G285" s="9" t="s">
         <v>447</v>
@@ -14114,7 +13621,7 @@
         <v>454</v>
       </c>
       <c r="F286" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G286" s="9" t="s">
         <v>447</v>
@@ -14137,7 +13644,7 @@
         <v>455</v>
       </c>
       <c r="F287" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G287" s="9" t="s">
         <v>447</v>
@@ -14160,7 +13667,7 @@
         <v>456</v>
       </c>
       <c r="F288" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G288" s="9" t="s">
         <v>447</v>
@@ -14183,7 +13690,7 @@
         <v>457</v>
       </c>
       <c r="F289" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G289" s="9" t="s">
         <v>447</v>
@@ -14206,7 +13713,7 @@
         <v>458</v>
       </c>
       <c r="F290" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G290" s="9" t="s">
         <v>459</v>
@@ -14229,7 +13736,7 @@
         <v>460</v>
       </c>
       <c r="F291" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G291" s="9" t="s">
         <v>459</v>
@@ -14252,7 +13759,7 @@
         <v>461</v>
       </c>
       <c r="F292" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G292" s="9" t="s">
         <v>459</v>
@@ -14275,7 +13782,7 @@
         <v>462</v>
       </c>
       <c r="F293" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G293" s="9" t="s">
         <v>447</v>
@@ -14298,7 +13805,7 @@
         <v>463</v>
       </c>
       <c r="F294" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G294" s="9" t="s">
         <v>459</v>
@@ -14321,7 +13828,7 @@
         <v>464</v>
       </c>
       <c r="F295" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G295" s="9" t="s">
         <v>459</v>
@@ -14344,7 +13851,7 @@
         <v>465</v>
       </c>
       <c r="F296" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G296" s="9" t="s">
         <v>459</v>
@@ -14367,7 +13874,7 @@
         <v>466</v>
       </c>
       <c r="F297" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G297" s="9" t="s">
         <v>459</v>
@@ -14390,7 +13897,7 @@
         <v>467</v>
       </c>
       <c r="F298" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G298" s="9" t="s">
         <v>459</v>
@@ -14413,7 +13920,7 @@
         <v>468</v>
       </c>
       <c r="F299" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G299" s="9" t="s">
         <v>459</v>
@@ -14436,7 +13943,7 @@
         <v>469</v>
       </c>
       <c r="F300" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G300" s="9" t="s">
         <v>459</v>
@@ -14459,7 +13966,7 @@
         <v>470</v>
       </c>
       <c r="F301" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G301" s="9" t="s">
         <v>459</v>
@@ -14482,7 +13989,7 @@
         <v>471</v>
       </c>
       <c r="F302" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G302" s="9" t="s">
         <v>459</v>
@@ -14505,7 +14012,7 @@
         <v>472</v>
       </c>
       <c r="F303" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G303" s="9" t="s">
         <v>459</v>
@@ -14528,7 +14035,7 @@
         <v>473</v>
       </c>
       <c r="F304" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G304" s="9" t="s">
         <v>459</v>
@@ -14551,7 +14058,7 @@
         <v>474</v>
       </c>
       <c r="F305" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G305" s="9" t="s">
         <v>459</v>
@@ -14574,7 +14081,7 @@
         <v>475</v>
       </c>
       <c r="F306" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G306" s="9" t="s">
         <v>459</v>
@@ -14827,7 +14334,7 @@
         <v>496</v>
       </c>
       <c r="F317" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G317" s="9" t="s">
         <v>497</v>
@@ -14850,7 +14357,7 @@
         <v>498</v>
       </c>
       <c r="F318" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G318" s="9" t="s">
         <v>497</v>
@@ -15356,7 +14863,7 @@
         <v>531</v>
       </c>
       <c r="F340" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G340" s="9" t="s">
         <v>532</v>
@@ -15400,7 +14907,7 @@
         <v>535</v>
       </c>
       <c r="F342" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G342" s="9" t="s">
         <v>536</v>
@@ -15423,7 +14930,7 @@
         <v>537</v>
       </c>
       <c r="F343" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G343" s="9" t="s">
         <v>536</v>
@@ -15446,7 +14953,7 @@
         <v>539</v>
       </c>
       <c r="F344" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G344" s="9" t="s">
         <v>540</v>
@@ -15492,7 +14999,7 @@
         <v>545</v>
       </c>
       <c r="F346" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G346" s="9" t="s">
         <v>546</v>
@@ -15515,7 +15022,7 @@
         <v>547</v>
       </c>
       <c r="F347" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G347" s="9" t="s">
         <v>546</v>
@@ -15538,7 +15045,7 @@
         <v>548</v>
       </c>
       <c r="F348" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G348" s="9" t="s">
         <v>546</v>
@@ -15561,7 +15068,7 @@
         <v>549</v>
       </c>
       <c r="F349" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G349" s="9" t="s">
         <v>546</v>
@@ -15670,7 +15177,7 @@
         <v>555</v>
       </c>
       <c r="F354" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G354" s="9" t="s">
         <v>546</v>
@@ -16178,7 +15685,7 @@
         <v>579</v>
       </c>
       <c r="F378" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G378" s="9" t="s">
         <v>546</v>
@@ -16222,7 +15729,7 @@
         <v>581</v>
       </c>
       <c r="F380" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G380" s="9" t="s">
         <v>546</v>
@@ -16245,7 +15752,7 @@
         <v>582</v>
       </c>
       <c r="F381" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G381" s="9" t="s">
         <v>546</v>
@@ -16268,7 +15775,7 @@
         <v>583</v>
       </c>
       <c r="F382" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G382" s="9" t="s">
         <v>546</v>
@@ -16291,7 +15798,7 @@
         <v>584</v>
       </c>
       <c r="F383" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G383" s="9" t="s">
         <v>546</v>
@@ -16381,7 +15888,7 @@
         <v>588</v>
       </c>
       <c r="F387" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G387" s="9" t="s">
         <v>546</v>
@@ -16404,7 +15911,7 @@
         <v>589</v>
       </c>
       <c r="F388" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G388" s="9" t="s">
         <v>546</v>
@@ -16450,7 +15957,7 @@
         <v>591</v>
       </c>
       <c r="F390" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G390" s="9" t="s">
         <v>546</v>
@@ -16473,7 +15980,7 @@
         <v>592</v>
       </c>
       <c r="F391" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G391" s="9" t="s">
         <v>546</v>
@@ -16496,7 +16003,7 @@
         <v>593</v>
       </c>
       <c r="F392" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G392" s="9" t="s">
         <v>546</v>
@@ -16519,7 +16026,7 @@
         <v>594</v>
       </c>
       <c r="F393" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G393" s="9" t="s">
         <v>546</v>
@@ -16542,7 +16049,7 @@
         <v>595</v>
       </c>
       <c r="F394" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G394" s="9" t="s">
         <v>546</v>
@@ -16565,7 +16072,7 @@
         <v>596</v>
       </c>
       <c r="F395" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G395" s="9" t="s">
         <v>546</v>
@@ -16588,7 +16095,7 @@
         <v>597</v>
       </c>
       <c r="F396" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G396" s="9" t="s">
         <v>546</v>
@@ -16611,7 +16118,7 @@
         <v>598</v>
       </c>
       <c r="F397" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G397" s="9" t="s">
         <v>546</v>
@@ -16634,7 +16141,7 @@
         <v>599</v>
       </c>
       <c r="F398" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G398" s="9" t="s">
         <v>546</v>
@@ -16657,7 +16164,7 @@
         <v>600</v>
       </c>
       <c r="F399" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G399" s="9" t="s">
         <v>546</v>
@@ -16871,7 +16378,7 @@
         <v>610</v>
       </c>
       <c r="F409" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G409" s="9" t="s">
         <v>546</v>
@@ -16894,7 +16401,7 @@
         <v>611</v>
       </c>
       <c r="F410" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G410" s="9" t="s">
         <v>546</v>
@@ -16917,7 +16424,7 @@
         <v>612</v>
       </c>
       <c r="F411" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G411" s="9" t="s">
         <v>546</v>
@@ -16940,7 +16447,7 @@
         <v>613</v>
       </c>
       <c r="F412" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G412" s="9" t="s">
         <v>546</v>
@@ -16963,7 +16470,7 @@
         <v>614</v>
       </c>
       <c r="F413" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G413" s="9" t="s">
         <v>546</v>
@@ -16986,7 +16493,7 @@
         <v>615</v>
       </c>
       <c r="F414" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G414" s="9" t="s">
         <v>546</v>
@@ -17009,7 +16516,7 @@
         <v>616</v>
       </c>
       <c r="F415" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G415" s="9" t="s">
         <v>546</v>
@@ -17032,7 +16539,7 @@
         <v>617</v>
       </c>
       <c r="F416" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G416" s="9" t="s">
         <v>546</v>
@@ -17055,7 +16562,7 @@
         <v>618</v>
       </c>
       <c r="F417" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G417" s="9" t="s">
         <v>546</v>
@@ -17078,7 +16585,7 @@
         <v>619</v>
       </c>
       <c r="F418" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G418" s="9" t="s">
         <v>546</v>
@@ -17101,7 +16608,7 @@
         <v>620</v>
       </c>
       <c r="F419" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G419" s="9" t="s">
         <v>546</v>
@@ -17124,7 +16631,7 @@
         <v>621</v>
       </c>
       <c r="F420" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G420" s="9" t="s">
         <v>546</v>
@@ -17147,7 +16654,7 @@
         <v>622</v>
       </c>
       <c r="F421" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G421" s="9" t="s">
         <v>546</v>
@@ -17170,7 +16677,7 @@
         <v>623</v>
       </c>
       <c r="F422" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G422" s="9" t="s">
         <v>546</v>
@@ -17193,7 +16700,7 @@
         <v>624</v>
       </c>
       <c r="F423" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G423" s="9" t="s">
         <v>546</v>
@@ -17216,7 +16723,7 @@
         <v>625</v>
       </c>
       <c r="F424" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G424" s="9" t="s">
         <v>546</v>
@@ -17239,7 +16746,7 @@
         <v>626</v>
       </c>
       <c r="F425" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G425" s="9" t="s">
         <v>546</v>
@@ -17262,7 +16769,7 @@
         <v>627</v>
       </c>
       <c r="F426" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G426" s="9" t="s">
         <v>546</v>
@@ -17285,7 +16792,7 @@
         <v>628</v>
       </c>
       <c r="F427" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G427" s="9" t="s">
         <v>546</v>
@@ -17308,7 +16815,7 @@
         <v>629</v>
       </c>
       <c r="F428" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G428" s="9" t="s">
         <v>546</v>
@@ -17331,7 +16838,7 @@
         <v>630</v>
       </c>
       <c r="F429" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G429" s="9" t="s">
         <v>546</v>
@@ -17354,7 +16861,7 @@
         <v>631</v>
       </c>
       <c r="F430" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G430" s="9" t="s">
         <v>546</v>
@@ -17377,7 +16884,7 @@
         <v>632</v>
       </c>
       <c r="F431" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G431" s="9" t="s">
         <v>546</v>
@@ -17400,7 +16907,7 @@
         <v>633</v>
       </c>
       <c r="F432" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G432" s="9" t="s">
         <v>546</v>
@@ -17423,7 +16930,7 @@
         <v>634</v>
       </c>
       <c r="F433" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G433" s="9" t="s">
         <v>546</v>
@@ -17446,7 +16953,7 @@
         <v>635</v>
       </c>
       <c r="F434" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G434" s="9" t="s">
         <v>546</v>
@@ -17469,7 +16976,7 @@
         <v>636</v>
       </c>
       <c r="F435" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G435" s="9" t="s">
         <v>546</v>
@@ -17492,7 +16999,7 @@
         <v>637</v>
       </c>
       <c r="F436" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G436" s="9" t="s">
         <v>546</v>
@@ -17515,7 +17022,7 @@
         <v>638</v>
       </c>
       <c r="F437" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G437" s="9" t="s">
         <v>546</v>
@@ -17538,7 +17045,7 @@
         <v>639</v>
       </c>
       <c r="F438" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G438" s="9" t="s">
         <v>546</v>
@@ -17561,7 +17068,7 @@
         <v>640</v>
       </c>
       <c r="F439" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G439" s="9" t="s">
         <v>546</v>
@@ -17584,7 +17091,7 @@
         <v>641</v>
       </c>
       <c r="F440" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G440" s="9" t="s">
         <v>546</v>
@@ -17607,7 +17114,7 @@
         <v>642</v>
       </c>
       <c r="F441" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G441" s="9" t="s">
         <v>546</v>
@@ -17630,7 +17137,7 @@
         <v>643</v>
       </c>
       <c r="F442" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G442" s="9" t="s">
         <v>546</v>
@@ -17653,7 +17160,7 @@
         <v>644</v>
       </c>
       <c r="F443" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G443" s="9" t="s">
         <v>546</v>
@@ -17676,7 +17183,7 @@
         <v>645</v>
       </c>
       <c r="F444" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G444" s="9" t="s">
         <v>546</v>
@@ -17699,7 +17206,7 @@
         <v>646</v>
       </c>
       <c r="F445" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G445" s="9" t="s">
         <v>546</v>
@@ -17722,7 +17229,7 @@
         <v>647</v>
       </c>
       <c r="F446" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G446" s="9" t="s">
         <v>546</v>
@@ -17766,7 +17273,7 @@
         <v>649</v>
       </c>
       <c r="F448" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G448" s="9" t="s">
         <v>650</v>
@@ -17789,7 +17296,7 @@
         <v>651</v>
       </c>
       <c r="F449" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G449" s="9" t="s">
         <v>650</v>
@@ -17812,7 +17319,7 @@
         <v>652</v>
       </c>
       <c r="F450" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G450" s="9" t="s">
         <v>650</v>
@@ -17858,7 +17365,7 @@
         <v>654</v>
       </c>
       <c r="F452" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G452" s="9" t="s">
         <v>546</v>
@@ -18038,7 +17545,7 @@
         <v>662</v>
       </c>
       <c r="F460" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G460" s="9" t="s">
         <v>546</v>
@@ -18145,7 +17652,7 @@
         <v>668</v>
       </c>
       <c r="F465" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G465" s="9" t="s">
         <v>669</v>
@@ -18336,7 +17843,7 @@
         <v>679</v>
       </c>
       <c r="F474" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G474" s="9" t="s">
         <v>680</v>
@@ -19073,7 +18580,7 @@
         <v>716</v>
       </c>
       <c r="F509" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G509" s="9" t="s">
         <v>717</v>
@@ -19096,7 +18603,7 @@
         <v>719</v>
       </c>
       <c r="F510" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G510" s="33" t="s">
         <v>720</v>
@@ -19119,7 +18626,7 @@
         <v>721</v>
       </c>
       <c r="F511" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G511" s="33" t="s">
         <v>720</v>
@@ -19142,7 +18649,7 @@
         <v>722</v>
       </c>
       <c r="F512" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G512" s="33" t="s">
         <v>720</v>
@@ -19165,7 +18672,7 @@
         <v>723</v>
       </c>
       <c r="F513" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G513" s="33" t="s">
         <v>720</v>
@@ -19188,7 +18695,7 @@
         <v>724</v>
       </c>
       <c r="F514" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G514" s="33" t="s">
         <v>720</v>
@@ -19211,7 +18718,7 @@
         <v>725</v>
       </c>
       <c r="F515" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G515" s="33" t="s">
         <v>726</v>
@@ -19234,7 +18741,7 @@
         <v>727</v>
       </c>
       <c r="F516" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G516" s="33" t="s">
         <v>726</v>
@@ -19257,7 +18764,7 @@
         <v>730</v>
       </c>
       <c r="F517" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G517" s="9" t="s">
         <v>731</v>
@@ -19303,7 +18810,7 @@
         <v>736</v>
       </c>
       <c r="F519" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G519" s="9"/>
     </row>
@@ -19324,7 +18831,7 @@
         <v>737</v>
       </c>
       <c r="F520" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G520" s="9" t="s">
         <v>131</v>
@@ -19347,7 +18854,7 @@
         <v>738</v>
       </c>
       <c r="F521" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G521" s="9" t="s">
         <v>131</v>
@@ -19370,7 +18877,7 @@
         <v>739</v>
       </c>
       <c r="F522" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G522" s="9" t="s">
         <v>131</v>
@@ -19393,7 +18900,7 @@
         <v>740</v>
       </c>
       <c r="F523" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G523" s="9" t="s">
         <v>131</v>
@@ -20025,7 +19532,7 @@
         <v>773</v>
       </c>
       <c r="F553" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G553" s="9" t="s">
         <v>774</v>
@@ -20048,7 +19555,7 @@
         <v>777</v>
       </c>
       <c r="F554" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G554" s="9" t="s">
         <v>778</v>
@@ -20071,7 +19578,7 @@
         <v>780</v>
       </c>
       <c r="F555" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G555" s="9" t="s">
         <v>781</v>
@@ -20094,7 +19601,7 @@
         <v>782</v>
       </c>
       <c r="F556" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G556" s="9" t="s">
         <v>781</v>
@@ -20117,7 +19624,7 @@
         <v>783</v>
       </c>
       <c r="F557" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G557" s="9" t="s">
         <v>781</v>
@@ -20140,7 +19647,7 @@
         <v>784</v>
       </c>
       <c r="F558" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G558" s="9" t="s">
         <v>781</v>
@@ -20163,7 +19670,7 @@
         <v>785</v>
       </c>
       <c r="F559" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G559" s="9" t="s">
         <v>781</v>
@@ -20186,7 +19693,7 @@
         <v>786</v>
       </c>
       <c r="F560" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G560" s="9" t="s">
         <v>781</v>
@@ -20209,7 +19716,7 @@
         <v>787</v>
       </c>
       <c r="F561" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G561" s="9" t="s">
         <v>781</v>
@@ -20232,7 +19739,7 @@
         <v>788</v>
       </c>
       <c r="F562" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G562" s="9" t="s">
         <v>781</v>
@@ -20255,7 +19762,7 @@
         <v>789</v>
       </c>
       <c r="F563" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G563" s="9" t="s">
         <v>781</v>
@@ -20278,7 +19785,7 @@
         <v>790</v>
       </c>
       <c r="F564" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G564" s="9" t="s">
         <v>781</v>
@@ -20301,7 +19808,7 @@
         <v>791</v>
       </c>
       <c r="F565" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G565" s="9" t="s">
         <v>781</v>
@@ -20324,7 +19831,7 @@
         <v>792</v>
       </c>
       <c r="F566" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G566" s="9" t="s">
         <v>781</v>
@@ -20347,7 +19854,7 @@
         <v>793</v>
       </c>
       <c r="F567" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G567" s="9" t="s">
         <v>781</v>
@@ -20370,7 +19877,7 @@
         <v>794</v>
       </c>
       <c r="F568" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G568" s="9" t="s">
         <v>781</v>
@@ -20393,7 +19900,7 @@
         <v>795</v>
       </c>
       <c r="F569" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G569" s="9" t="s">
         <v>781</v>
@@ -20416,7 +19923,7 @@
         <v>796</v>
       </c>
       <c r="F570" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G570" s="9" t="s">
         <v>781</v>
@@ -20439,7 +19946,7 @@
         <v>797</v>
       </c>
       <c r="F571" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G571" s="9" t="s">
         <v>781</v>
@@ -20462,7 +19969,7 @@
         <v>798</v>
       </c>
       <c r="F572" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G572" s="9" t="s">
         <v>781</v>
@@ -20485,7 +19992,7 @@
         <v>799</v>
       </c>
       <c r="F573" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G573" s="9" t="s">
         <v>781</v>
@@ -20508,7 +20015,7 @@
         <v>800</v>
       </c>
       <c r="F574" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G574" s="9" t="s">
         <v>781</v>
@@ -20531,7 +20038,7 @@
         <v>801</v>
       </c>
       <c r="F575" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G575" s="9" t="s">
         <v>781</v>
@@ -20554,7 +20061,7 @@
         <v>802</v>
       </c>
       <c r="F576" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G576" s="9" t="s">
         <v>781</v>
@@ -20577,7 +20084,7 @@
         <v>804</v>
       </c>
       <c r="F577" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G577" s="9" t="s">
         <v>805</v>
@@ -20600,7 +20107,7 @@
         <v>807</v>
       </c>
       <c r="F578" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G578" s="9" t="s">
         <v>808</v>
@@ -20738,7 +20245,7 @@
         <v>820</v>
       </c>
       <c r="F584" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G584" s="9" t="s">
         <v>821</v>
@@ -20807,7 +20314,7 @@
         <v>828</v>
       </c>
       <c r="F587" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G587" s="33" t="s">
         <v>829</v>
@@ -20830,7 +20337,7 @@
         <v>830</v>
       </c>
       <c r="F588" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G588" s="33" t="s">
         <v>829</v>
@@ -20853,7 +20360,7 @@
         <v>831</v>
       </c>
       <c r="F589" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G589" s="33" t="s">
         <v>829</v>
@@ -20899,7 +20406,7 @@
         <v>835</v>
       </c>
       <c r="F591" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G591" s="16" t="s">
         <v>836</v>
@@ -20922,7 +20429,7 @@
         <v>838</v>
       </c>
       <c r="F592" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G592" s="20" t="s">
         <v>839</v>
@@ -20945,7 +20452,7 @@
         <v>840</v>
       </c>
       <c r="F593" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G593" s="20" t="s">
         <v>839</v>
@@ -20968,7 +20475,7 @@
         <v>841</v>
       </c>
       <c r="F594" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G594" s="20" t="s">
         <v>839</v>
@@ -20991,7 +20498,7 @@
         <v>842</v>
       </c>
       <c r="F595" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G595" s="20" t="s">
         <v>839</v>
@@ -21014,7 +20521,7 @@
         <v>843</v>
       </c>
       <c r="F596" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G596" s="20" t="s">
         <v>839</v>
@@ -21037,7 +20544,7 @@
         <v>844</v>
       </c>
       <c r="F597" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G597" s="20" t="s">
         <v>839</v>
@@ -21060,7 +20567,7 @@
         <v>845</v>
       </c>
       <c r="F598" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G598" s="20" t="s">
         <v>839</v>
@@ -21083,7 +20590,7 @@
         <v>846</v>
       </c>
       <c r="F599" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G599" s="20" t="s">
         <v>839</v>
@@ -21106,7 +20613,7 @@
         <v>847</v>
       </c>
       <c r="F600" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G600" s="20" t="s">
         <v>839</v>
@@ -21129,7 +20636,7 @@
         <v>848</v>
       </c>
       <c r="F601" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G601" s="20" t="s">
         <v>839</v>
@@ -21152,7 +20659,7 @@
         <v>849</v>
       </c>
       <c r="F602" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G602" s="20" t="s">
         <v>839</v>
@@ -21175,7 +20682,7 @@
         <v>850</v>
       </c>
       <c r="F603" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G603" s="20" t="s">
         <v>839</v>
@@ -21198,7 +20705,7 @@
         <v>851</v>
       </c>
       <c r="F604" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G604" s="20" t="s">
         <v>839</v>
@@ -21221,7 +20728,7 @@
         <v>852</v>
       </c>
       <c r="F605" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G605" s="20" t="s">
         <v>839</v>
@@ -21244,7 +20751,7 @@
         <v>853</v>
       </c>
       <c r="F606" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G606" s="20" t="s">
         <v>839</v>
@@ -21267,7 +20774,7 @@
         <v>854</v>
       </c>
       <c r="F607" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G607" s="20" t="s">
         <v>839</v>
@@ -21290,7 +20797,7 @@
         <v>855</v>
       </c>
       <c r="F608" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G608" s="20" t="s">
         <v>839</v>
@@ -21313,7 +20820,7 @@
         <v>856</v>
       </c>
       <c r="F609" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G609" s="20" t="s">
         <v>839</v>
@@ -21336,7 +20843,7 @@
         <v>857</v>
       </c>
       <c r="F610" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G610" s="20" t="s">
         <v>839</v>
@@ -21359,7 +20866,7 @@
         <v>858</v>
       </c>
       <c r="F611" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G611" s="20" t="s">
         <v>839</v>
@@ -21382,7 +20889,7 @@
         <v>859</v>
       </c>
       <c r="F612" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G612" s="20" t="s">
         <v>839</v>
@@ -21405,7 +20912,7 @@
         <v>860</v>
       </c>
       <c r="F613" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G613" s="20" t="s">
         <v>839</v>
@@ -21428,7 +20935,7 @@
         <v>861</v>
       </c>
       <c r="F614" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G614" s="20" t="s">
         <v>839</v>
@@ -21451,7 +20958,7 @@
         <v>862</v>
       </c>
       <c r="F615" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G615" s="20" t="s">
         <v>839</v>
@@ -21474,7 +20981,7 @@
         <v>863</v>
       </c>
       <c r="F616" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G616" s="20" t="s">
         <v>839</v>
@@ -21497,7 +21004,7 @@
         <v>864</v>
       </c>
       <c r="F617" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G617" s="20" t="s">
         <v>839</v>
@@ -21520,7 +21027,7 @@
         <v>865</v>
       </c>
       <c r="F618" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G618" s="20" t="s">
         <v>839</v>
@@ -21543,7 +21050,7 @@
         <v>867</v>
       </c>
       <c r="F619" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G619" s="9" t="s">
         <v>781</v>
@@ -21566,7 +21073,7 @@
         <v>870</v>
       </c>
       <c r="F620" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G620" s="16" t="s">
         <v>871</v>
@@ -21589,7 +21096,7 @@
         <v>872</v>
       </c>
       <c r="F621" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G621" s="16" t="s">
         <v>871</v>
@@ -21612,7 +21119,7 @@
         <v>873</v>
       </c>
       <c r="F622" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G622" s="16" t="s">
         <v>871</v>
@@ -21635,7 +21142,7 @@
         <v>874</v>
       </c>
       <c r="F623" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G623" s="16" t="s">
         <v>875</v>
@@ -21658,7 +21165,7 @@
         <v>876</v>
       </c>
       <c r="F624" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G624" s="16" t="s">
         <v>875</v>
@@ -21681,7 +21188,7 @@
         <v>877</v>
       </c>
       <c r="F625" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G625" s="16" t="s">
         <v>875</v>
@@ -21704,7 +21211,7 @@
         <v>878</v>
       </c>
       <c r="F626" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G626" s="16" t="s">
         <v>875</v>
@@ -21727,7 +21234,7 @@
         <v>879</v>
       </c>
       <c r="F627" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G627" s="16" t="s">
         <v>871</v>
@@ -21750,7 +21257,7 @@
         <v>880</v>
       </c>
       <c r="F628" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G628" s="16" t="s">
         <v>875</v>
@@ -21773,7 +21280,7 @@
         <v>881</v>
       </c>
       <c r="F629" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G629" s="16" t="s">
         <v>875</v>
@@ -21796,7 +21303,7 @@
         <v>882</v>
       </c>
       <c r="F630" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G630" s="16" t="s">
         <v>875</v>
@@ -21819,7 +21326,7 @@
         <v>883</v>
       </c>
       <c r="F631" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G631" s="16" t="s">
         <v>871</v>
@@ -21842,7 +21349,7 @@
         <v>884</v>
       </c>
       <c r="F632" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G632" s="16" t="s">
         <v>871</v>
@@ -21865,7 +21372,7 @@
         <v>885</v>
       </c>
       <c r="F633" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G633" s="16" t="s">
         <v>871</v>
@@ -21934,7 +21441,7 @@
         <v>892</v>
       </c>
       <c r="F636" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G636" s="33" t="s">
         <v>893</v>
@@ -21957,7 +21464,7 @@
         <v>894</v>
       </c>
       <c r="F637" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G637" s="33" t="s">
         <v>893</v>
@@ -21980,7 +21487,7 @@
         <v>895</v>
       </c>
       <c r="F638" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G638" s="33" t="s">
         <v>893</v>
@@ -22026,7 +21533,7 @@
         <v>901</v>
       </c>
       <c r="F640" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G640" s="9" t="s">
         <v>902</v>
@@ -22049,7 +21556,7 @@
         <v>903</v>
       </c>
       <c r="F641" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G641" s="9" t="s">
         <v>902</v>
@@ -22072,7 +21579,7 @@
         <v>904</v>
       </c>
       <c r="F642" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G642" s="9" t="s">
         <v>902</v>
@@ -22095,7 +21602,7 @@
         <v>905</v>
       </c>
       <c r="F643" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G643" s="9" t="s">
         <v>902</v>
@@ -22141,7 +21648,7 @@
         <v>911</v>
       </c>
       <c r="F645" s="7" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
       <c r="G645" s="9" t="s">
         <v>912</v>
@@ -22164,7 +21671,7 @@
         <v>913</v>
       </c>
       <c r="F646" s="7" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
       <c r="G646" s="9" t="s">
         <v>912</v>
@@ -22187,7 +21694,7 @@
         <v>914</v>
       </c>
       <c r="F647" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G647" s="9" t="s">
         <v>915</v>
@@ -22210,7 +21717,7 @@
         <v>916</v>
       </c>
       <c r="F648" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G648" s="9" t="s">
         <v>915</v>
@@ -22233,7 +21740,7 @@
         <v>917</v>
       </c>
       <c r="F649" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G649" s="9" t="s">
         <v>915</v>
@@ -22256,7 +21763,7 @@
         <v>918</v>
       </c>
       <c r="F650" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G650" s="9" t="s">
         <v>915</v>
@@ -22390,7 +21897,7 @@
         <v>925</v>
       </c>
       <c r="F656" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G656" s="33" t="s">
         <v>926</v>
@@ -24614,7 +24121,7 @@
         <v>1032</v>
       </c>
       <c r="F760" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G760" s="27" t="s">
         <v>1033</v>
@@ -24936,7 +24443,7 @@
         <v>1047</v>
       </c>
       <c r="F774" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G774" s="27" t="s">
         <v>1048</v>
@@ -26477,7 +25984,7 @@
         <v>1119</v>
       </c>
       <c r="F841" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G841" s="9" t="s">
         <v>1120</v>
@@ -26523,7 +26030,7 @@
         <v>1122</v>
       </c>
       <c r="F843" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G843" s="9" t="s">
         <v>1120</v>
@@ -26569,7 +26076,7 @@
         <v>1124</v>
       </c>
       <c r="F845" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G845" s="9" t="s">
         <v>1120</v>
@@ -26592,7 +26099,7 @@
         <v>1125</v>
       </c>
       <c r="F846" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G846" s="9" t="s">
         <v>1126</v>
@@ -26615,7 +26122,7 @@
         <v>1127</v>
       </c>
       <c r="F847" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G847" s="9" t="s">
         <v>1126</v>
@@ -26638,7 +26145,7 @@
         <v>1128</v>
       </c>
       <c r="F848" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G848" s="9" t="s">
         <v>1126</v>
@@ -26661,7 +26168,7 @@
         <v>1129</v>
       </c>
       <c r="F849" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G849" s="9" t="s">
         <v>1126</v>
@@ -26684,7 +26191,7 @@
         <v>1130</v>
       </c>
       <c r="F850" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G850" s="9" t="s">
         <v>1126</v>
@@ -26707,7 +26214,7 @@
         <v>1131</v>
       </c>
       <c r="F851" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G851" s="9" t="s">
         <v>1126</v>
@@ -26730,7 +26237,7 @@
         <v>1132</v>
       </c>
       <c r="F852" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G852" s="9" t="s">
         <v>1120</v>
@@ -26753,7 +26260,7 @@
         <v>1133</v>
       </c>
       <c r="F853" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G853" s="9" t="s">
         <v>1126</v>
@@ -26914,7 +26421,7 @@
         <v>1150</v>
       </c>
       <c r="F860" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G860" s="9" t="s">
         <v>1151</v>
@@ -26937,7 +26444,7 @@
         <v>1152</v>
       </c>
       <c r="F861" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G861" s="9" t="s">
         <v>1151</v>
@@ -26960,7 +26467,7 @@
         <v>1153</v>
       </c>
       <c r="F862" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G862" s="9" t="s">
         <v>1151</v>
@@ -26983,7 +26490,7 @@
         <v>1155</v>
       </c>
       <c r="F863" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G863" s="9" t="s">
         <v>1156</v>
@@ -27006,7 +26513,7 @@
         <v>1158</v>
       </c>
       <c r="F864" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G864" s="9"/>
     </row>
@@ -27027,7 +26534,7 @@
         <v>1159</v>
       </c>
       <c r="F865" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G865" s="9"/>
     </row>
@@ -27048,7 +26555,7 @@
         <v>1160</v>
       </c>
       <c r="F866" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G866" s="9"/>
     </row>
@@ -27069,7 +26576,7 @@
         <v>1161</v>
       </c>
       <c r="F867" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G867" s="9"/>
     </row>
@@ -27090,7 +26597,7 @@
         <v>1163</v>
       </c>
       <c r="F868" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G868" s="9" t="s">
         <v>1164</v>
@@ -27113,7 +26620,7 @@
         <v>1165</v>
       </c>
       <c r="F869" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G869" s="9" t="s">
         <v>1164</v>
@@ -27136,7 +26643,7 @@
         <v>1166</v>
       </c>
       <c r="F870" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G870" s="9" t="s">
         <v>1164</v>
@@ -27159,7 +26666,7 @@
         <v>1169</v>
       </c>
       <c r="F871" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G871" s="9" t="s">
         <v>131</v>
@@ -27182,7 +26689,7 @@
         <v>1170</v>
       </c>
       <c r="F872" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G872" s="9" t="s">
         <v>131</v>
@@ -27205,7 +26712,7 @@
         <v>1171</v>
       </c>
       <c r="F873" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G873" s="9" t="s">
         <v>131</v>
@@ -27228,7 +26735,7 @@
         <v>1172</v>
       </c>
       <c r="F874" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G874" s="9" t="s">
         <v>131</v>
@@ -27251,7 +26758,7 @@
         <v>1173</v>
       </c>
       <c r="F875" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G875" s="9" t="s">
         <v>131</v>
@@ -27274,7 +26781,7 @@
         <v>1174</v>
       </c>
       <c r="F876" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G876" s="9" t="s">
         <v>131</v>
@@ -27297,7 +26804,7 @@
         <v>1175</v>
       </c>
       <c r="F877" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G877" s="9" t="s">
         <v>131</v>
@@ -27320,7 +26827,7 @@
         <v>1176</v>
       </c>
       <c r="F878" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G878" s="9" t="s">
         <v>131</v>
@@ -27343,7 +26850,7 @@
         <v>1177</v>
       </c>
       <c r="F879" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G879" s="9" t="s">
         <v>131</v>
@@ -27366,7 +26873,7 @@
         <v>1178</v>
       </c>
       <c r="F880" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G880" s="9" t="s">
         <v>131</v>
@@ -27389,7 +26896,7 @@
         <v>1179</v>
       </c>
       <c r="F881" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G881" s="9" t="s">
         <v>131</v>
@@ -27412,7 +26919,7 @@
         <v>1180</v>
       </c>
       <c r="F882" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G882" s="9" t="s">
         <v>131</v>
@@ -27435,7 +26942,7 @@
         <v>1181</v>
       </c>
       <c r="F883" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G883" s="9" t="s">
         <v>131</v>
@@ -27458,7 +26965,7 @@
         <v>1182</v>
       </c>
       <c r="F884" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G884" s="9" t="s">
         <v>131</v>
@@ -27481,7 +26988,7 @@
         <v>1184</v>
       </c>
       <c r="F885" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G885" s="9" t="s">
         <v>1185</v>
@@ -27504,7 +27011,7 @@
         <v>1186</v>
       </c>
       <c r="F886" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G886" s="9" t="s">
         <v>1187</v>
@@ -27527,7 +27034,7 @@
         <v>1189</v>
       </c>
       <c r="F887" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G887" s="33" t="s">
         <v>1190</v>
@@ -27550,7 +27057,7 @@
         <v>1191</v>
       </c>
       <c r="F888" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G888" s="33" t="s">
         <v>1190</v>
@@ -27573,7 +27080,7 @@
         <v>1192</v>
       </c>
       <c r="F889" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G889" s="33" t="s">
         <v>1190</v>
@@ -27596,7 +27103,7 @@
         <v>1193</v>
       </c>
       <c r="F890" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G890" s="33" t="s">
         <v>1190</v>
@@ -27619,7 +27126,7 @@
         <v>1194</v>
       </c>
       <c r="F891" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G891" s="33" t="s">
         <v>1190</v>
@@ -27642,7 +27149,7 @@
         <v>1195</v>
       </c>
       <c r="F892" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G892" s="33" t="s">
         <v>1190</v>
@@ -27665,7 +27172,7 @@
         <v>1196</v>
       </c>
       <c r="F893" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G893" s="9" t="s">
         <v>1197</v>
@@ -27688,7 +27195,7 @@
         <v>1198</v>
       </c>
       <c r="F894" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G894" s="33" t="s">
         <v>1190</v>
@@ -27872,7 +27379,7 @@
         <v>1213</v>
       </c>
       <c r="F902" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G902" s="9" t="s">
         <v>131</v>
@@ -27895,7 +27402,7 @@
         <v>1214</v>
       </c>
       <c r="F903" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G903" s="9" t="s">
         <v>131</v>
@@ -28079,7 +27586,7 @@
         <v>1229</v>
       </c>
       <c r="F911" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G911" s="9" t="s">
         <v>1230</v>
@@ -29367,7 +28874,7 @@
         <v>1314</v>
       </c>
       <c r="F967" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="G967" s="9" t="s">
         <v>1315</v>
